--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/after_conversion_xian_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/after_conversion_xian_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="682">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>W1</t>
@@ -2420,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD281"/>
+  <dimension ref="A1:AE281"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2447,9 +2450,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2540,10 +2544,13 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="B2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>31.79</v>
@@ -2552,13 +2559,13 @@
         <v>100.25</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L2">
         <v>21.08912739393014</v>
@@ -2588,9 +2595,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>31.79</v>
@@ -2599,13 +2606,13 @@
         <v>100.25</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L3">
         <v>30.17535714645276</v>
@@ -2635,9 +2642,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>31.79</v>
@@ -2646,13 +2653,13 @@
         <v>100.25</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L4">
         <v>23.5265234288435</v>
@@ -2682,9 +2689,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>31.76</v>
@@ -2693,13 +2700,13 @@
         <v>100.29</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L5">
         <v>3.800171659854208</v>
@@ -2729,9 +2736,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>31.58</v>
@@ -2740,13 +2747,13 @@
         <v>100.43</v>
       </c>
       <c r="H6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L6">
         <v>9.284507592562823</v>
@@ -2776,18 +2783,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="B7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L7">
         <v>9.156566566862834</v>
@@ -2817,9 +2824,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>31.54</v>
@@ -2828,13 +2835,13 @@
         <v>100.46</v>
       </c>
       <c r="H8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L8">
         <v>43.67995747258725</v>
@@ -2864,9 +2871,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>31.54</v>
@@ -2875,13 +2882,13 @@
         <v>100.46</v>
       </c>
       <c r="H9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L9">
         <v>40.75096193078116</v>
@@ -2911,9 +2918,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="B10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>31.54</v>
@@ -2922,13 +2929,13 @@
         <v>100.46</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L10">
         <v>43.15379554873063</v>
@@ -2958,9 +2965,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>31.58</v>
@@ -2969,13 +2976,13 @@
         <v>100.72</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L11">
         <v>34.09802421490964</v>
@@ -3005,9 +3012,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="B12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>31.58</v>
@@ -3016,13 +3023,13 @@
         <v>100.72</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L12">
         <v>49.94566776598221</v>
@@ -3052,9 +3059,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="B13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>31.27</v>
@@ -3063,13 +3070,13 @@
         <v>100.8</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J13" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L13">
         <v>51.14694707191191</v>
@@ -3099,9 +3106,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="B14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>31.27</v>
@@ -3110,13 +3117,13 @@
         <v>100.8</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J14" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L14">
         <v>53.75440846080464</v>
@@ -3146,9 +3153,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="B15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>31.27</v>
@@ -3157,13 +3164,13 @@
         <v>100.8</v>
       </c>
       <c r="H15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J15" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L15">
         <v>50.93398407458446</v>
@@ -3193,9 +3200,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>31.27</v>
@@ -3204,13 +3211,13 @@
         <v>100.8</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J16" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L16">
         <v>54.5028208271944</v>
@@ -3242,7 +3249,7 @@
     </row>
     <row r="17" spans="2:30">
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>31.27</v>
@@ -3251,13 +3258,13 @@
         <v>100.8</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J17" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L17">
         <v>72.18358139847477</v>
@@ -3286,7 +3293,7 @@
     </row>
     <row r="18" spans="2:30">
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18">
         <v>31.27</v>
@@ -3295,13 +3302,13 @@
         <v>100.8</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J18" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L18">
         <v>57.86291136048107</v>
@@ -3333,7 +3340,7 @@
     </row>
     <row r="19" spans="2:30">
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19">
         <v>31.27</v>
@@ -3342,13 +3349,13 @@
         <v>100.8</v>
       </c>
       <c r="H19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L19">
         <v>62.98254506095643</v>
@@ -3380,7 +3387,7 @@
     </row>
     <row r="20" spans="2:30">
       <c r="B20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <v>31.33</v>
@@ -3389,13 +3396,13 @@
         <v>100.9</v>
       </c>
       <c r="H20" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" t="s">
         <v>92</v>
       </c>
-      <c r="I20" t="s">
-        <v>91</v>
-      </c>
       <c r="J20" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L20">
         <v>45.35822527011936</v>
@@ -3427,7 +3434,7 @@
     </row>
     <row r="21" spans="2:30">
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21">
         <v>31.33</v>
@@ -3436,13 +3443,13 @@
         <v>100.9</v>
       </c>
       <c r="H21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J21" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L21">
         <v>43.39014530096036</v>
@@ -3474,7 +3481,7 @@
     </row>
     <row r="22" spans="2:30">
       <c r="B22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22">
         <v>31.17</v>
@@ -3483,13 +3490,13 @@
         <v>100.92</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J22" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L22">
         <v>46.3990218896764</v>
@@ -3521,7 +3528,7 @@
     </row>
     <row r="23" spans="2:30">
       <c r="B23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>31.17</v>
@@ -3530,13 +3537,13 @@
         <v>100.92</v>
       </c>
       <c r="H23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J23" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L23">
         <v>54.3225280397232</v>
@@ -3568,7 +3575,7 @@
     </row>
     <row r="24" spans="2:30">
       <c r="B24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>31.17</v>
@@ -3577,13 +3584,13 @@
         <v>100.92</v>
       </c>
       <c r="H24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I24" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J24" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L24">
         <v>57.22557557830984</v>
@@ -3615,7 +3622,7 @@
     </row>
     <row r="25" spans="2:30">
       <c r="B25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25">
         <v>31.17</v>
@@ -3624,13 +3631,13 @@
         <v>100.92</v>
       </c>
       <c r="H25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I25" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J25" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L25">
         <v>48.9158630719127</v>
@@ -3662,7 +3669,7 @@
     </row>
     <row r="26" spans="2:30">
       <c r="B26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26">
         <v>31.08</v>
@@ -3671,13 +3678,13 @@
         <v>101.01</v>
       </c>
       <c r="H26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J26" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L26">
         <v>44.80676537016727</v>
@@ -3709,7 +3716,7 @@
     </row>
     <row r="27" spans="2:30">
       <c r="B27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C27">
         <v>31.08</v>
@@ -3718,13 +3725,13 @@
         <v>101.01</v>
       </c>
       <c r="H27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I27" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J27" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L27">
         <v>46.47068321954421</v>
@@ -3756,7 +3763,7 @@
     </row>
     <row r="28" spans="2:30">
       <c r="B28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28">
         <v>31.08</v>
@@ -3765,13 +3772,13 @@
         <v>101.01</v>
       </c>
       <c r="H28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J28" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L28">
         <v>46.96139688012546</v>
@@ -3803,7 +3810,7 @@
     </row>
     <row r="29" spans="2:30">
       <c r="B29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29">
         <v>31.07</v>
@@ -3812,13 +3819,13 @@
         <v>101.02</v>
       </c>
       <c r="H29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L29">
         <v>49.77192785496188</v>
@@ -3850,7 +3857,7 @@
     </row>
     <row r="30" spans="2:30">
       <c r="B30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30">
         <v>31.01</v>
@@ -3859,13 +3866,13 @@
         <v>101.08</v>
       </c>
       <c r="H30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L30">
         <v>24.95566663728924</v>
@@ -3897,7 +3904,7 @@
     </row>
     <row r="31" spans="2:30">
       <c r="B31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31">
         <v>31.01</v>
@@ -3906,13 +3913,13 @@
         <v>101.08</v>
       </c>
       <c r="H31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I31" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J31" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L31">
         <v>24.84880023099017</v>
@@ -3944,7 +3951,7 @@
     </row>
     <row r="32" spans="2:30">
       <c r="B32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C32">
         <v>31.01</v>
@@ -3953,13 +3960,13 @@
         <v>101.08</v>
       </c>
       <c r="H32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I32" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J32" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L32">
         <v>24.54390391256988</v>
@@ -3991,7 +3998,7 @@
     </row>
     <row r="33" spans="2:30">
       <c r="B33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C33">
         <v>31.06</v>
@@ -4000,13 +4007,13 @@
         <v>101.1</v>
       </c>
       <c r="H33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L33">
         <v>48.3837744064822</v>
@@ -4038,7 +4045,7 @@
     </row>
     <row r="34" spans="2:30">
       <c r="B34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C34">
         <v>31.06</v>
@@ -4047,13 +4054,13 @@
         <v>101.1</v>
       </c>
       <c r="H34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I34" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J34" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L34">
         <v>50.29572292657652</v>
@@ -4085,7 +4092,7 @@
     </row>
     <row r="35" spans="2:30">
       <c r="B35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>31.06</v>
@@ -4094,13 +4101,13 @@
         <v>101.1</v>
       </c>
       <c r="H35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I35" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J35" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L35">
         <v>50.4336057927952</v>
@@ -4132,7 +4139,7 @@
     </row>
     <row r="36" spans="2:30">
       <c r="B36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36">
         <v>31.06</v>
@@ -4141,13 +4148,13 @@
         <v>101.1</v>
       </c>
       <c r="H36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J36" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L36">
         <v>49.18214967451161</v>
@@ -4179,7 +4186,7 @@
     </row>
     <row r="37" spans="2:30">
       <c r="B37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C37">
         <v>31.06</v>
@@ -4188,13 +4195,13 @@
         <v>101.1</v>
       </c>
       <c r="H37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I37" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J37" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L37">
         <v>46.86202286356115</v>
@@ -4226,7 +4233,7 @@
     </row>
     <row r="38" spans="2:30">
       <c r="B38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C38">
         <v>31.18</v>
@@ -4235,13 +4242,13 @@
         <v>101.17</v>
       </c>
       <c r="H38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I38" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J38" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L38">
         <v>20.94581035913522</v>
@@ -4273,7 +4280,7 @@
     </row>
     <row r="39" spans="2:30">
       <c r="B39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C39">
         <v>31.18</v>
@@ -4282,13 +4289,13 @@
         <v>101.17</v>
       </c>
       <c r="H39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I39" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J39" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L39">
         <v>20.18934961750644</v>
@@ -4320,7 +4327,7 @@
     </row>
     <row r="40" spans="2:30">
       <c r="B40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C40">
         <v>31.28</v>
@@ -4329,13 +4336,13 @@
         <v>101.18</v>
       </c>
       <c r="H40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I40" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J40" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L40">
         <v>28.17387725878928</v>
@@ -4367,7 +4374,7 @@
     </row>
     <row r="41" spans="2:30">
       <c r="B41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C41">
         <v>31.28</v>
@@ -4376,13 +4383,13 @@
         <v>101.18</v>
       </c>
       <c r="H41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I41" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J41" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L41">
         <v>26.76027041300777</v>
@@ -4414,7 +4421,7 @@
     </row>
     <row r="42" spans="2:30">
       <c r="B42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C42">
         <v>31.14</v>
@@ -4423,13 +4430,13 @@
         <v>101.18</v>
       </c>
       <c r="H42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I42" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J42" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L42">
         <v>20.13137269535984</v>
@@ -4461,7 +4468,7 @@
     </row>
     <row r="43" spans="2:30">
       <c r="B43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>31.14</v>
@@ -4470,13 +4477,13 @@
         <v>101.18</v>
       </c>
       <c r="H43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I43" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J43" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L43">
         <v>18.19704262029214</v>
@@ -4508,7 +4515,7 @@
     </row>
     <row r="44" spans="2:30">
       <c r="B44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>30.95</v>
@@ -4517,13 +4524,13 @@
         <v>101.24</v>
       </c>
       <c r="H44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I44" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J44" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L44">
         <v>75.57117322625511</v>
@@ -4555,7 +4562,7 @@
     </row>
     <row r="45" spans="2:30">
       <c r="B45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C45">
         <v>30.95</v>
@@ -4564,13 +4571,13 @@
         <v>101.24</v>
       </c>
       <c r="H45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J45" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L45">
         <v>75.30040236140272</v>
@@ -4602,7 +4609,7 @@
     </row>
     <row r="46" spans="2:30">
       <c r="B46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C46">
         <v>30.95</v>
@@ -4611,13 +4618,13 @@
         <v>101.24</v>
       </c>
       <c r="H46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I46" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J46" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L46">
         <v>80.55946803506168</v>
@@ -4649,7 +4656,7 @@
     </row>
     <row r="47" spans="2:30">
       <c r="B47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C47">
         <v>30.95</v>
@@ -4658,13 +4665,13 @@
         <v>101.24</v>
       </c>
       <c r="H47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I47" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J47" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L47">
         <v>81.89838659479847</v>
@@ -4696,7 +4703,7 @@
     </row>
     <row r="48" spans="2:30">
       <c r="B48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C48">
         <v>30.95</v>
@@ -4705,13 +4712,13 @@
         <v>101.24</v>
       </c>
       <c r="H48" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J48" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L48">
         <v>80.34621659094329</v>
@@ -4743,7 +4750,7 @@
     </row>
     <row r="49" spans="2:30">
       <c r="B49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C49">
         <v>30.95</v>
@@ -4752,13 +4759,13 @@
         <v>101.24</v>
       </c>
       <c r="H49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I49" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J49" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L49">
         <v>75.19674051325606</v>
@@ -4790,7 +4797,7 @@
     </row>
     <row r="50" spans="2:30">
       <c r="B50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C50">
         <v>30.95</v>
@@ -4799,13 +4806,13 @@
         <v>101.24</v>
       </c>
       <c r="H50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I50" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J50" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L50">
         <v>23.5189138980576</v>
@@ -4837,7 +4844,7 @@
     </row>
     <row r="51" spans="2:30">
       <c r="B51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C51">
         <v>30.95</v>
@@ -4846,13 +4853,13 @@
         <v>101.24</v>
       </c>
       <c r="H51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J51" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L51">
         <v>21.63620190903845</v>
@@ -4884,7 +4891,7 @@
     </row>
     <row r="52" spans="2:30">
       <c r="B52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C52">
         <v>30.95</v>
@@ -4893,13 +4900,13 @@
         <v>101.24</v>
       </c>
       <c r="H52" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J52" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L52">
         <v>21.0468944762325</v>
@@ -4931,7 +4938,7 @@
     </row>
     <row r="53" spans="2:30">
       <c r="B53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C53">
         <v>30.95</v>
@@ -4940,13 +4947,13 @@
         <v>101.24</v>
       </c>
       <c r="H53" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J53" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L53">
         <v>20.73729514742257</v>
@@ -4978,7 +4985,7 @@
     </row>
     <row r="54" spans="2:30">
       <c r="B54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C54">
         <v>30.95</v>
@@ -4987,13 +4994,13 @@
         <v>101.24</v>
       </c>
       <c r="H54" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J54" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L54">
         <v>23.11448821824018</v>
@@ -5025,7 +5032,7 @@
     </row>
     <row r="55" spans="2:30">
       <c r="B55" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C55">
         <v>30.95</v>
@@ -5034,13 +5041,13 @@
         <v>101.24</v>
       </c>
       <c r="H55" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J55" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L55">
         <v>18.76707898009298</v>
@@ -5072,7 +5079,7 @@
     </row>
     <row r="56" spans="2:30">
       <c r="B56" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C56">
         <v>30.95</v>
@@ -5081,13 +5088,13 @@
         <v>101.24</v>
       </c>
       <c r="H56" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J56" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L56">
         <v>25.53348354146977</v>
@@ -5119,7 +5126,7 @@
     </row>
     <row r="57" spans="2:30">
       <c r="B57" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C57">
         <v>30.95</v>
@@ -5128,13 +5135,13 @@
         <v>101.24</v>
       </c>
       <c r="H57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J57" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L57">
         <v>28.53373201124357</v>
@@ -5166,7 +5173,7 @@
     </row>
     <row r="58" spans="2:30">
       <c r="B58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C58">
         <v>30.95</v>
@@ -5175,13 +5182,13 @@
         <v>101.24</v>
       </c>
       <c r="H58" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I58" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J58" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L58">
         <v>27.9385085597912</v>
@@ -5213,7 +5220,7 @@
     </row>
     <row r="59" spans="2:30">
       <c r="B59" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C59">
         <v>30.95</v>
@@ -5222,13 +5229,13 @@
         <v>101.24</v>
       </c>
       <c r="H59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J59" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L59">
         <v>29.30694801309367</v>
@@ -5260,7 +5267,7 @@
     </row>
     <row r="60" spans="2:30">
       <c r="B60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C60">
         <v>30.95</v>
@@ -5269,13 +5276,13 @@
         <v>101.24</v>
       </c>
       <c r="H60" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J60" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L60">
         <v>27.0973519169432</v>
@@ -5307,7 +5314,7 @@
     </row>
     <row r="61" spans="2:30">
       <c r="B61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C61">
         <v>30.95</v>
@@ -5316,13 +5323,13 @@
         <v>101.24</v>
       </c>
       <c r="H61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J61" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L61">
         <v>28.18672603981994</v>
@@ -5354,7 +5361,7 @@
     </row>
     <row r="62" spans="2:30">
       <c r="B62" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C62">
         <v>30.95</v>
@@ -5363,13 +5370,13 @@
         <v>101.24</v>
       </c>
       <c r="H62" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J62" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L62">
         <v>27.90429096702293</v>
@@ -5401,7 +5408,7 @@
     </row>
     <row r="63" spans="2:30">
       <c r="B63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C63">
         <v>30.95</v>
@@ -5410,13 +5417,13 @@
         <v>101.24</v>
       </c>
       <c r="H63" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J63" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L63">
         <v>27.11962028598113</v>
@@ -5448,7 +5455,7 @@
     </row>
     <row r="64" spans="2:30">
       <c r="B64" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C64">
         <v>30.95</v>
@@ -5457,13 +5464,13 @@
         <v>101.24</v>
       </c>
       <c r="H64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J64" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L64">
         <v>26.8331093354449</v>
@@ -5495,7 +5502,7 @@
     </row>
     <row r="65" spans="2:30">
       <c r="B65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C65">
         <v>30.95</v>
@@ -5504,13 +5511,13 @@
         <v>101.24</v>
       </c>
       <c r="H65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J65" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L65">
         <v>26.85381716780866</v>
@@ -5542,7 +5549,7 @@
     </row>
     <row r="66" spans="2:30">
       <c r="B66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C66">
         <v>30.95</v>
@@ -5551,13 +5558,13 @@
         <v>101.24</v>
       </c>
       <c r="H66" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J66" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L66">
         <v>19.86669245036554</v>
@@ -5589,7 +5596,7 @@
     </row>
     <row r="67" spans="2:30">
       <c r="B67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C67">
         <v>30.95</v>
@@ -5598,13 +5605,13 @@
         <v>101.24</v>
       </c>
       <c r="H67" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J67" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L67">
         <v>28.329894269076</v>
@@ -5636,7 +5643,7 @@
     </row>
     <row r="68" spans="2:30">
       <c r="B68" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C68">
         <v>30.95</v>
@@ -5645,13 +5652,13 @@
         <v>101.24</v>
       </c>
       <c r="H68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J68" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L68">
         <v>32.3108392039136</v>
@@ -5683,7 +5690,7 @@
     </row>
     <row r="69" spans="2:30">
       <c r="B69" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C69">
         <v>30.95</v>
@@ -5692,13 +5699,13 @@
         <v>101.24</v>
       </c>
       <c r="H69" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I69" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J69" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L69">
         <v>23.04590686925087</v>
@@ -5730,7 +5737,7 @@
     </row>
     <row r="70" spans="2:30">
       <c r="B70" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C70">
         <v>30.95</v>
@@ -5739,13 +5746,13 @@
         <v>101.24</v>
       </c>
       <c r="H70" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I70" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J70" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L70">
         <v>31.79981769246117</v>
@@ -5777,7 +5784,7 @@
     </row>
     <row r="71" spans="2:30">
       <c r="B71" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C71">
         <v>30.95</v>
@@ -5786,13 +5793,13 @@
         <v>101.24</v>
       </c>
       <c r="H71" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I71" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J71" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L71">
         <v>29.22244276946949</v>
@@ -5824,7 +5831,7 @@
     </row>
     <row r="72" spans="2:30">
       <c r="B72" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C72">
         <v>30.86</v>
@@ -5833,13 +5840,13 @@
         <v>101.29</v>
       </c>
       <c r="H72" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I72" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J72" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L72">
         <v>17.8635493199819</v>
@@ -5871,7 +5878,7 @@
     </row>
     <row r="73" spans="2:30">
       <c r="B73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C73">
         <v>30.86</v>
@@ -5880,13 +5887,13 @@
         <v>101.29</v>
       </c>
       <c r="H73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I73" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J73" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L73">
         <v>18.14970120813148</v>
@@ -5918,7 +5925,7 @@
     </row>
     <row r="74" spans="2:30">
       <c r="B74" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C74">
         <v>30.86</v>
@@ -5927,13 +5934,13 @@
         <v>101.29</v>
       </c>
       <c r="H74" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I74" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J74" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L74">
         <v>24.81478423606316</v>
@@ -5965,7 +5972,7 @@
     </row>
     <row r="75" spans="2:30">
       <c r="B75" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C75">
         <v>30.86</v>
@@ -5974,13 +5981,13 @@
         <v>101.29</v>
       </c>
       <c r="H75" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I75" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J75" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L75">
         <v>24.13106836583459</v>
@@ -6012,7 +6019,7 @@
     </row>
     <row r="76" spans="2:30">
       <c r="B76" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C76">
         <v>30.86</v>
@@ -6021,13 +6028,13 @@
         <v>101.29</v>
       </c>
       <c r="H76" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I76" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J76" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L76">
         <v>25.0251369848728</v>
@@ -6059,7 +6066,7 @@
     </row>
     <row r="77" spans="2:30">
       <c r="B77" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C77">
         <v>31.04</v>
@@ -6068,13 +6075,13 @@
         <v>101.4</v>
       </c>
       <c r="H77" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I77" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J77" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L77">
         <v>25.09750910627882</v>
@@ -6106,7 +6113,7 @@
     </row>
     <row r="78" spans="2:30">
       <c r="B78" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C78">
         <v>30.49</v>
@@ -6115,13 +6122,13 @@
         <v>101.53</v>
       </c>
       <c r="H78" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I78" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J78" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L78">
         <v>25.81480632619078</v>
@@ -6153,7 +6160,7 @@
     </row>
     <row r="79" spans="2:30">
       <c r="B79" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C79">
         <v>30.49</v>
@@ -6162,13 +6169,13 @@
         <v>101.53</v>
       </c>
       <c r="H79" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J79" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L79">
         <v>29.82416625277004</v>
@@ -6200,7 +6207,7 @@
     </row>
     <row r="80" spans="2:30">
       <c r="B80" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C80">
         <v>30.49</v>
@@ -6209,13 +6216,13 @@
         <v>101.53</v>
       </c>
       <c r="H80" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I80" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J80" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L80">
         <v>22.81208914193508</v>
@@ -6247,7 +6254,7 @@
     </row>
     <row r="81" spans="2:30">
       <c r="B81" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C81">
         <v>30.54</v>
@@ -6256,13 +6263,13 @@
         <v>101.62</v>
       </c>
       <c r="H81" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I81" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J81" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L81">
         <v>45.96861249873792</v>
@@ -6294,7 +6301,7 @@
     </row>
     <row r="82" spans="2:30">
       <c r="B82" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C82">
         <v>30.54</v>
@@ -6303,13 +6310,13 @@
         <v>101.62</v>
       </c>
       <c r="H82" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I82" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J82" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L82">
         <v>44.32547214922285</v>
@@ -6341,7 +6348,7 @@
     </row>
     <row r="83" spans="2:30">
       <c r="B83" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C83">
         <v>30.54</v>
@@ -6350,13 +6357,13 @@
         <v>101.62</v>
       </c>
       <c r="H83" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I83" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J83" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L83">
         <v>48.09923536518973</v>
@@ -6388,7 +6395,7 @@
     </row>
     <row r="84" spans="2:30">
       <c r="B84" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C84">
         <v>30.54</v>
@@ -6397,13 +6404,13 @@
         <v>101.62</v>
       </c>
       <c r="H84" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I84" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J84" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L84">
         <v>64.72470340259186</v>
@@ -6435,7 +6442,7 @@
     </row>
     <row r="85" spans="2:30">
       <c r="B85" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C85">
         <v>30.54</v>
@@ -6444,13 +6451,13 @@
         <v>101.62</v>
       </c>
       <c r="H85" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I85" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J85" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L85">
         <v>46.45969263668794</v>
@@ -6482,7 +6489,7 @@
     </row>
     <row r="86" spans="2:30">
       <c r="B86" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C86">
         <v>30.54</v>
@@ -6491,13 +6498,13 @@
         <v>101.62</v>
       </c>
       <c r="H86" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I86" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J86" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L86">
         <v>50.14575301081393</v>
@@ -6529,7 +6536,7 @@
     </row>
     <row r="87" spans="2:30">
       <c r="B87" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C87">
         <v>30.54</v>
@@ -6538,13 +6545,13 @@
         <v>101.62</v>
       </c>
       <c r="H87" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I87" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J87" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L87">
         <v>49.94079672434388</v>
@@ -6576,7 +6583,7 @@
     </row>
     <row r="88" spans="2:30">
       <c r="B88" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C88">
         <v>30.54</v>
@@ -6585,13 +6592,13 @@
         <v>101.62</v>
       </c>
       <c r="H88" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J88" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L88">
         <v>52.01871336357467</v>
@@ -6623,7 +6630,7 @@
     </row>
     <row r="89" spans="2:30">
       <c r="B89" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C89">
         <v>30.54</v>
@@ -6632,13 +6639,13 @@
         <v>101.62</v>
       </c>
       <c r="H89" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I89" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J89" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L89">
         <v>50.64903072945874</v>
@@ -6670,7 +6677,7 @@
     </row>
     <row r="90" spans="2:30">
       <c r="B90" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C90">
         <v>30.54</v>
@@ -6679,13 +6686,13 @@
         <v>101.62</v>
       </c>
       <c r="H90" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J90" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L90">
         <v>46.71018124316134</v>
@@ -6717,7 +6724,7 @@
     </row>
     <row r="91" spans="2:30">
       <c r="B91" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C91">
         <v>30.54</v>
@@ -6726,13 +6733,13 @@
         <v>101.62</v>
       </c>
       <c r="H91" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I91" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J91" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L91">
         <v>48.85167546641829</v>
@@ -6764,7 +6771,7 @@
     </row>
     <row r="92" spans="2:30">
       <c r="B92" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C92">
         <v>30.54</v>
@@ -6773,13 +6780,13 @@
         <v>101.62</v>
       </c>
       <c r="H92" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I92" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J92" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L92">
         <v>53.84898981334889</v>
@@ -6811,7 +6818,7 @@
     </row>
     <row r="93" spans="2:30">
       <c r="B93" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C93">
         <v>30.55</v>
@@ -6820,13 +6827,13 @@
         <v>101.62</v>
       </c>
       <c r="H93" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I93" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J93" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L93">
         <v>30.02882038022353</v>
@@ -6858,7 +6865,7 @@
     </row>
     <row r="94" spans="2:30">
       <c r="B94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C94">
         <v>30.55</v>
@@ -6867,13 +6874,13 @@
         <v>101.62</v>
       </c>
       <c r="H94" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I94" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J94" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L94">
         <v>27.75405170611547</v>
@@ -6905,7 +6912,7 @@
     </row>
     <row r="95" spans="2:30">
       <c r="B95" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C95">
         <v>30.55</v>
@@ -6914,13 +6921,13 @@
         <v>101.62</v>
       </c>
       <c r="H95" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I95" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J95" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L95">
         <v>28.42240053404458</v>
@@ -6952,7 +6959,7 @@
     </row>
     <row r="96" spans="2:30">
       <c r="B96" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C96">
         <v>30.55</v>
@@ -6961,13 +6968,13 @@
         <v>101.62</v>
       </c>
       <c r="H96" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I96" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J96" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L96">
         <v>28.48982609057824</v>
@@ -6999,7 +7006,7 @@
     </row>
     <row r="97" spans="2:30">
       <c r="B97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C97">
         <v>30.55</v>
@@ -7008,13 +7015,13 @@
         <v>101.62</v>
       </c>
       <c r="H97" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I97" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J97" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L97">
         <v>26.43934516635763</v>
@@ -7046,7 +7053,7 @@
     </row>
     <row r="98" spans="2:30">
       <c r="B98" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C98">
         <v>30.55</v>
@@ -7055,13 +7062,13 @@
         <v>101.62</v>
       </c>
       <c r="H98" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I98" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J98" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L98">
         <v>26.68120899788228</v>
@@ -7093,7 +7100,7 @@
     </row>
     <row r="99" spans="2:30">
       <c r="B99" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C99">
         <v>30.28</v>
@@ -7102,13 +7109,13 @@
         <v>101.84</v>
       </c>
       <c r="H99" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I99" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J99" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L99">
         <v>19.94011618903403</v>
@@ -7140,7 +7147,7 @@
     </row>
     <row r="100" spans="2:30">
       <c r="B100" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C100">
         <v>30.28</v>
@@ -7149,13 +7156,13 @@
         <v>101.84</v>
       </c>
       <c r="H100" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I100" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J100" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L100">
         <v>19.91890457973786</v>
@@ -7187,7 +7194,7 @@
     </row>
     <row r="101" spans="2:30">
       <c r="B101" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C101">
         <v>30.28</v>
@@ -7196,13 +7203,13 @@
         <v>101.84</v>
       </c>
       <c r="H101" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I101" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J101" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L101">
         <v>26.69533811770494</v>
@@ -7234,7 +7241,7 @@
     </row>
     <row r="102" spans="2:30">
       <c r="B102" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C102">
         <v>30.28</v>
@@ -7243,13 +7250,13 @@
         <v>101.84</v>
       </c>
       <c r="H102" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I102" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J102" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L102">
         <v>22.10911744057313</v>
@@ -7281,7 +7288,7 @@
     </row>
     <row r="103" spans="2:30">
       <c r="B103" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C103">
         <v>30.01</v>
@@ -7290,13 +7297,13 @@
         <v>101.86</v>
       </c>
       <c r="H103" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I103" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J103" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L103">
         <v>15.37468474539939</v>
@@ -7328,7 +7335,7 @@
     </row>
     <row r="104" spans="2:30">
       <c r="B104" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C104">
         <v>30.01</v>
@@ -7337,13 +7344,13 @@
         <v>101.86</v>
       </c>
       <c r="H104" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I104" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J104" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L104">
         <v>15.77542948217157</v>
@@ -7375,7 +7382,7 @@
     </row>
     <row r="105" spans="2:30">
       <c r="B105" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C105">
         <v>30.01</v>
@@ -7384,13 +7391,13 @@
         <v>101.86</v>
       </c>
       <c r="H105" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I105" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J105" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L105">
         <v>15.324651072666</v>
@@ -7422,7 +7429,7 @@
     </row>
     <row r="106" spans="2:30">
       <c r="B106" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C106">
         <v>30.01</v>
@@ -7431,13 +7438,13 @@
         <v>101.86</v>
       </c>
       <c r="H106" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I106" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J106" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L106">
         <v>14.72650366224622</v>
@@ -7469,7 +7476,7 @@
     </row>
     <row r="107" spans="2:30">
       <c r="B107" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C107">
         <v>30.01</v>
@@ -7478,13 +7485,13 @@
         <v>101.86</v>
       </c>
       <c r="H107" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I107" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J107" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L107">
         <v>17.05837829938186</v>
@@ -7516,7 +7523,7 @@
     </row>
     <row r="108" spans="2:30">
       <c r="B108" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C108">
         <v>30.01</v>
@@ -7525,13 +7532,13 @@
         <v>101.86</v>
       </c>
       <c r="H108" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I108" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J108" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L108">
         <v>17.24110005926685</v>
@@ -7563,7 +7570,7 @@
     </row>
     <row r="109" spans="2:30">
       <c r="B109" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C109">
         <v>30.01</v>
@@ -7572,13 +7579,13 @@
         <v>101.86</v>
       </c>
       <c r="H109" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I109" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J109" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L109">
         <v>20.40773391211248</v>
@@ -7610,7 +7617,7 @@
     </row>
     <row r="110" spans="2:30">
       <c r="B110" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C110">
         <v>30.01</v>
@@ -7619,13 +7626,13 @@
         <v>101.86</v>
       </c>
       <c r="H110" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I110" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J110" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L110">
         <v>15.89232627543878</v>
@@ -7654,7 +7661,7 @@
     </row>
     <row r="111" spans="2:30">
       <c r="B111" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C111">
         <v>30.01</v>
@@ -7663,13 +7670,13 @@
         <v>101.86</v>
       </c>
       <c r="H111" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I111" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J111" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L111">
         <v>19.88592875771332</v>
@@ -7698,7 +7705,7 @@
     </row>
     <row r="112" spans="2:30">
       <c r="B112" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C112">
         <v>30.01</v>
@@ -7707,13 +7714,13 @@
         <v>101.86</v>
       </c>
       <c r="H112" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I112" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J112" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L112">
         <v>17.89329009996987</v>
@@ -7745,7 +7752,7 @@
     </row>
     <row r="113" spans="2:30">
       <c r="B113" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C113">
         <v>30.01</v>
@@ -7754,13 +7761,13 @@
         <v>101.86</v>
       </c>
       <c r="H113" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I113" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J113" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L113">
         <v>14.54303389227583</v>
@@ -7792,7 +7799,7 @@
     </row>
     <row r="114" spans="2:30">
       <c r="B114" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C114">
         <v>30.01</v>
@@ -7801,13 +7808,13 @@
         <v>101.86</v>
       </c>
       <c r="H114" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I114" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J114" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L114">
         <v>13.83545767169392</v>
@@ -7839,7 +7846,7 @@
     </row>
     <row r="115" spans="2:30">
       <c r="B115" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C115">
         <v>30.01</v>
@@ -7848,13 +7855,13 @@
         <v>101.86</v>
       </c>
       <c r="H115" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I115" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J115" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L115">
         <v>13.68584320311183</v>
@@ -7886,7 +7893,7 @@
     </row>
     <row r="116" spans="2:30">
       <c r="B116" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C116">
         <v>30.01</v>
@@ -7895,13 +7902,13 @@
         <v>101.86</v>
       </c>
       <c r="H116" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I116" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J116" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L116">
         <v>12.45591353194765</v>
@@ -7933,7 +7940,7 @@
     </row>
     <row r="117" spans="2:30">
       <c r="B117" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C117">
         <v>30.01</v>
@@ -7942,13 +7949,13 @@
         <v>101.86</v>
       </c>
       <c r="H117" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I117" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J117" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L117">
         <v>11.91756507055086</v>
@@ -7980,7 +7987,7 @@
     </row>
     <row r="118" spans="2:30">
       <c r="B118" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C118">
         <v>30.01</v>
@@ -7989,13 +7996,13 @@
         <v>101.86</v>
       </c>
       <c r="H118" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I118" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J118" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L118">
         <v>11.95563513025457</v>
@@ -8027,7 +8034,7 @@
     </row>
     <row r="119" spans="2:30">
       <c r="B119" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C119">
         <v>30.27</v>
@@ -8036,13 +8043,13 @@
         <v>101.87</v>
       </c>
       <c r="H119" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I119" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J119" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L119">
         <v>31.43017399141223</v>
@@ -8074,7 +8081,7 @@
     </row>
     <row r="120" spans="2:30">
       <c r="B120" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C120">
         <v>30.27</v>
@@ -8083,13 +8090,13 @@
         <v>101.87</v>
       </c>
       <c r="H120" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I120" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J120" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L120">
         <v>31.91622050186521</v>
@@ -8121,7 +8128,7 @@
     </row>
     <row r="121" spans="2:30">
       <c r="B121" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C121">
         <v>30.27</v>
@@ -8130,13 +8137,13 @@
         <v>101.87</v>
       </c>
       <c r="H121" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I121" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J121" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L121">
         <v>30.58032625066713</v>
@@ -8168,7 +8175,7 @@
     </row>
     <row r="122" spans="2:30">
       <c r="B122" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C122">
         <v>30.27</v>
@@ -8177,13 +8184,13 @@
         <v>101.87</v>
       </c>
       <c r="H122" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I122" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J122" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L122">
         <v>31.56037030341515</v>
@@ -8215,7 +8222,7 @@
     </row>
     <row r="123" spans="2:30">
       <c r="B123" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C123">
         <v>30.27</v>
@@ -8224,13 +8231,13 @@
         <v>101.87</v>
       </c>
       <c r="H123" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I123" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J123" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L123">
         <v>31.39232432341603</v>
@@ -8262,7 +8269,7 @@
     </row>
     <row r="124" spans="2:30">
       <c r="B124" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C124">
         <v>30.27</v>
@@ -8271,13 +8278,13 @@
         <v>101.87</v>
       </c>
       <c r="H124" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I124" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J124" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L124">
         <v>34.80167828725119</v>
@@ -8309,7 +8316,7 @@
     </row>
     <row r="125" spans="2:30">
       <c r="B125" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C125">
         <v>30.27</v>
@@ -8318,13 +8325,13 @@
         <v>101.87</v>
       </c>
       <c r="H125" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I125" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J125" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L125">
         <v>33.57288310214656</v>
@@ -8356,7 +8363,7 @@
     </row>
     <row r="126" spans="2:30">
       <c r="B126" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C126">
         <v>30.17</v>
@@ -8365,13 +8372,13 @@
         <v>101.87</v>
       </c>
       <c r="H126" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I126" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J126" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L126">
         <v>19.50268381687432</v>
@@ -8403,7 +8410,7 @@
     </row>
     <row r="127" spans="2:30">
       <c r="B127" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C127">
         <v>30.17</v>
@@ -8412,13 +8419,13 @@
         <v>101.87</v>
       </c>
       <c r="H127" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I127" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J127" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L127">
         <v>14.13379194238786</v>
@@ -8450,7 +8457,7 @@
     </row>
     <row r="128" spans="2:30">
       <c r="B128" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C128">
         <v>30.17</v>
@@ -8459,13 +8466,13 @@
         <v>101.87</v>
       </c>
       <c r="H128" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I128" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J128" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L128">
         <v>14.86104959320223</v>
@@ -8497,7 +8504,7 @@
     </row>
     <row r="129" spans="2:30">
       <c r="B129" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C129">
         <v>30.17</v>
@@ -8506,13 +8513,13 @@
         <v>101.87</v>
       </c>
       <c r="H129" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I129" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J129" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L129">
         <v>16.36581357255476</v>
@@ -8544,7 +8551,7 @@
     </row>
     <row r="130" spans="2:30">
       <c r="B130" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C130">
         <v>30.17</v>
@@ -8553,13 +8560,13 @@
         <v>101.87</v>
       </c>
       <c r="H130" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I130" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J130" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L130">
         <v>16.00363576596058</v>
@@ -8591,7 +8598,7 @@
     </row>
     <row r="131" spans="2:30">
       <c r="B131" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C131">
         <v>30.17</v>
@@ -8600,13 +8607,13 @@
         <v>101.87</v>
       </c>
       <c r="H131" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I131" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J131" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L131">
         <v>15.29552520276536</v>
@@ -8638,7 +8645,7 @@
     </row>
     <row r="132" spans="2:30">
       <c r="B132" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C132">
         <v>30.17</v>
@@ -8647,13 +8654,13 @@
         <v>101.87</v>
       </c>
       <c r="H132" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I132" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J132" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L132">
         <v>14.71565146556761</v>
@@ -8685,7 +8692,7 @@
     </row>
     <row r="133" spans="2:30">
       <c r="B133" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C133">
         <v>30.25</v>
@@ -8694,13 +8701,13 @@
         <v>101.88</v>
       </c>
       <c r="H133" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I133" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J133" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L133">
         <v>38.57739178662635</v>
@@ -8732,7 +8739,7 @@
     </row>
     <row r="134" spans="2:30">
       <c r="B134" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C134">
         <v>30.25</v>
@@ -8741,13 +8748,13 @@
         <v>101.88</v>
       </c>
       <c r="H134" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I134" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J134" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L134">
         <v>43.14857177812642</v>
@@ -8779,7 +8786,7 @@
     </row>
     <row r="135" spans="2:30">
       <c r="B135" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C135">
         <v>30.25</v>
@@ -8788,13 +8795,13 @@
         <v>101.88</v>
       </c>
       <c r="H135" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I135" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J135" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L135">
         <v>35.89813581589569</v>
@@ -8826,7 +8833,7 @@
     </row>
     <row r="136" spans="2:30">
       <c r="B136" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C136">
         <v>30.25</v>
@@ -8835,13 +8842,13 @@
         <v>101.88</v>
       </c>
       <c r="H136" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I136" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J136" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L136">
         <v>42.29939734360386</v>
@@ -8873,7 +8880,7 @@
     </row>
     <row r="137" spans="2:30">
       <c r="B137" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C137">
         <v>30.25</v>
@@ -8882,13 +8889,13 @@
         <v>101.88</v>
       </c>
       <c r="H137" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I137" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J137" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L137">
         <v>34.97558353986742</v>
@@ -8920,7 +8927,7 @@
     </row>
     <row r="138" spans="2:30">
       <c r="B138" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C138">
         <v>30.25</v>
@@ -8929,13 +8936,13 @@
         <v>101.88</v>
       </c>
       <c r="H138" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I138" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J138" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L138">
         <v>35.20488780920999</v>
@@ -8967,7 +8974,7 @@
     </row>
     <row r="139" spans="2:30">
       <c r="B139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C139">
         <v>30.25</v>
@@ -8976,13 +8983,13 @@
         <v>101.88</v>
       </c>
       <c r="H139" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I139" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J139" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L139">
         <v>36.94026931577904</v>
@@ -9014,7 +9021,7 @@
     </row>
     <row r="140" spans="2:30">
       <c r="B140" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C140">
         <v>30.25</v>
@@ -9023,13 +9030,13 @@
         <v>101.88</v>
       </c>
       <c r="H140" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I140" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J140" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L140">
         <v>36.72433380528662</v>
@@ -9061,7 +9068,7 @@
     </row>
     <row r="141" spans="2:30">
       <c r="B141" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C141">
         <v>30.25</v>
@@ -9070,13 +9077,13 @@
         <v>101.88</v>
       </c>
       <c r="H141" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I141" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J141" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L141">
         <v>42.43279652002134</v>
@@ -9108,7 +9115,7 @@
     </row>
     <row r="142" spans="2:30">
       <c r="B142" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C142">
         <v>30.25</v>
@@ -9117,13 +9124,13 @@
         <v>101.88</v>
       </c>
       <c r="H142" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I142" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J142" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L142">
         <v>35.14699980791524</v>
@@ -9155,7 +9162,7 @@
     </row>
     <row r="143" spans="2:30">
       <c r="B143" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C143">
         <v>30.09</v>
@@ -9164,13 +9171,13 @@
         <v>101.95</v>
       </c>
       <c r="H143" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I143" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J143" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L143">
         <v>19.21331012207732</v>
@@ -9202,7 +9209,7 @@
     </row>
     <row r="144" spans="2:30">
       <c r="B144" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C144">
         <v>30.09</v>
@@ -9211,13 +9218,13 @@
         <v>101.95</v>
       </c>
       <c r="H144" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I144" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J144" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L144">
         <v>20.47218400300838</v>
@@ -9249,7 +9256,7 @@
     </row>
     <row r="145" spans="2:30">
       <c r="B145" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C145">
         <v>30.09</v>
@@ -9258,13 +9265,13 @@
         <v>101.95</v>
       </c>
       <c r="H145" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I145" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J145" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L145">
         <v>20.47261199020694</v>
@@ -9296,7 +9303,7 @@
     </row>
     <row r="146" spans="2:30">
       <c r="B146" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C146">
         <v>30.09</v>
@@ -9305,13 +9312,13 @@
         <v>101.95</v>
       </c>
       <c r="H146" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I146" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J146" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L146">
         <v>20.85292113558878</v>
@@ -9343,7 +9350,7 @@
     </row>
     <row r="147" spans="2:30">
       <c r="B147" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C147">
         <v>30.09</v>
@@ -9352,13 +9359,13 @@
         <v>101.95</v>
       </c>
       <c r="H147" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I147" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J147" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L147">
         <v>20.6698662483309</v>
@@ -9390,7 +9397,7 @@
     </row>
     <row r="148" spans="2:30">
       <c r="B148" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C148">
         <v>30.09</v>
@@ -9399,13 +9406,13 @@
         <v>101.95</v>
       </c>
       <c r="H148" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I148" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J148" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L148">
         <v>16.81169943740878</v>
@@ -9437,7 +9444,7 @@
     </row>
     <row r="149" spans="2:30">
       <c r="B149" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C149">
         <v>30.09</v>
@@ -9446,13 +9453,13 @@
         <v>101.95</v>
       </c>
       <c r="H149" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I149" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J149" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L149">
         <v>24.58016645722712</v>
@@ -9484,7 +9491,7 @@
     </row>
     <row r="150" spans="2:30">
       <c r="B150" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C150">
         <v>30.09</v>
@@ -9493,13 +9500,13 @@
         <v>101.95</v>
       </c>
       <c r="H150" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I150" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J150" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L150">
         <v>26.2651347292516</v>
@@ -9531,7 +9538,7 @@
     </row>
     <row r="151" spans="2:30">
       <c r="B151" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C151">
         <v>30.09</v>
@@ -9540,13 +9547,13 @@
         <v>101.95</v>
       </c>
       <c r="H151" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I151" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J151" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L151">
         <v>25.63945761782982</v>
@@ -9578,7 +9585,7 @@
     </row>
     <row r="152" spans="2:30">
       <c r="B152" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C152">
         <v>30.09</v>
@@ -9587,13 +9594,13 @@
         <v>101.95</v>
       </c>
       <c r="H152" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I152" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J152" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L152">
         <v>24.871581113323</v>
@@ -9625,7 +9632,7 @@
     </row>
     <row r="153" spans="2:30">
       <c r="B153" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C153">
         <v>30.09</v>
@@ -9634,13 +9641,13 @@
         <v>101.95</v>
       </c>
       <c r="H153" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I153" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J153" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L153">
         <v>31.48348317121073</v>
@@ -9672,7 +9679,7 @@
     </row>
     <row r="154" spans="2:30">
       <c r="B154" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C154">
         <v>30.09</v>
@@ -9681,13 +9688,13 @@
         <v>101.95</v>
       </c>
       <c r="H154" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I154" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J154" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L154">
         <v>35.30311445726263</v>
@@ -9719,7 +9726,7 @@
     </row>
     <row r="155" spans="2:30">
       <c r="B155" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C155">
         <v>30.09</v>
@@ -9728,13 +9735,13 @@
         <v>101.95</v>
       </c>
       <c r="H155" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I155" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J155" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L155">
         <v>34.61896775627811</v>
@@ -9766,7 +9773,7 @@
     </row>
     <row r="156" spans="2:30">
       <c r="B156" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C156">
         <v>30.09</v>
@@ -9775,13 +9782,13 @@
         <v>101.95</v>
       </c>
       <c r="H156" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I156" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J156" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L156">
         <v>35.07729219870466</v>
@@ -9813,7 +9820,7 @@
     </row>
     <row r="157" spans="2:30">
       <c r="B157" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C157">
         <v>30.09</v>
@@ -9822,13 +9829,13 @@
         <v>101.95</v>
       </c>
       <c r="H157" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I157" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J157" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L157">
         <v>32.02940883478603</v>
@@ -9860,7 +9867,7 @@
     </row>
     <row r="158" spans="2:30">
       <c r="B158" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C158">
         <v>30.09</v>
@@ -9869,13 +9876,13 @@
         <v>101.95</v>
       </c>
       <c r="H158" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I158" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J158" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L158">
         <v>31.25435801743152</v>
@@ -9907,7 +9914,7 @@
     </row>
     <row r="159" spans="2:30">
       <c r="B159" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C159">
         <v>30.09</v>
@@ -9916,13 +9923,13 @@
         <v>101.95</v>
       </c>
       <c r="H159" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I159" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J159" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L159">
         <v>34.74057152859355</v>
@@ -9954,7 +9961,7 @@
     </row>
     <row r="160" spans="2:30">
       <c r="B160" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C160">
         <v>29.98</v>
@@ -9963,13 +9970,13 @@
         <v>101.96</v>
       </c>
       <c r="H160" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I160" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J160" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L160">
         <v>51.25714951000029</v>
@@ -10001,7 +10008,7 @@
     </row>
     <row r="161" spans="2:30">
       <c r="B161" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C161">
         <v>29.98</v>
@@ -10010,13 +10017,13 @@
         <v>101.96</v>
       </c>
       <c r="H161" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I161" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J161" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L161">
         <v>52.26794372431828</v>
@@ -10048,7 +10055,7 @@
     </row>
     <row r="162" spans="2:30">
       <c r="B162" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C162">
         <v>29.98</v>
@@ -10057,13 +10064,13 @@
         <v>101.96</v>
       </c>
       <c r="H162" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I162" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J162" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L162">
         <v>51.15838844159588</v>
@@ -10095,7 +10102,7 @@
     </row>
     <row r="163" spans="2:30">
       <c r="B163" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C163">
         <v>29.98</v>
@@ -10104,13 +10111,13 @@
         <v>101.96</v>
       </c>
       <c r="H163" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I163" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J163" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L163">
         <v>51.87120090395762</v>
@@ -10142,7 +10149,7 @@
     </row>
     <row r="164" spans="2:30">
       <c r="B164" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C164">
         <v>29.98</v>
@@ -10151,13 +10158,13 @@
         <v>101.96</v>
       </c>
       <c r="H164" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I164" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J164" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L164">
         <v>49.33417311210406</v>
@@ -10189,7 +10196,7 @@
     </row>
     <row r="165" spans="2:30">
       <c r="B165" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C165">
         <v>29.98</v>
@@ -10198,13 +10205,13 @@
         <v>101.96</v>
       </c>
       <c r="H165" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I165" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J165" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L165">
         <v>53.26960565338417</v>
@@ -10236,7 +10243,7 @@
     </row>
     <row r="166" spans="2:30">
       <c r="B166" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C166">
         <v>29.98</v>
@@ -10245,13 +10252,13 @@
         <v>101.96</v>
       </c>
       <c r="H166" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I166" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J166" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L166">
         <v>56.27597677482076</v>
@@ -10283,7 +10290,7 @@
     </row>
     <row r="167" spans="2:30">
       <c r="B167" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C167">
         <v>29.98</v>
@@ -10292,13 +10299,13 @@
         <v>101.96</v>
       </c>
       <c r="H167" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I167" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J167" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L167">
         <v>53.55576121341085</v>
@@ -10330,7 +10337,7 @@
     </row>
     <row r="168" spans="2:30">
       <c r="B168" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C168">
         <v>29.98</v>
@@ -10339,13 +10346,13 @@
         <v>101.96</v>
       </c>
       <c r="H168" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I168" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J168" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L168">
         <v>53.93662923031994</v>
@@ -10377,7 +10384,7 @@
     </row>
     <row r="169" spans="2:30">
       <c r="B169" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C169">
         <v>29.98</v>
@@ -10386,13 +10393,13 @@
         <v>101.96</v>
       </c>
       <c r="H169" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I169" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J169" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L169">
         <v>51.24279277927307</v>
@@ -10424,7 +10431,7 @@
     </row>
     <row r="170" spans="2:30">
       <c r="B170" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C170">
         <v>29.98</v>
@@ -10433,13 +10440,13 @@
         <v>101.96</v>
       </c>
       <c r="H170" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I170" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J170" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L170">
         <v>53.19231091790983</v>
@@ -10471,7 +10478,7 @@
     </row>
     <row r="171" spans="2:30">
       <c r="B171" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C171">
         <v>29.98</v>
@@ -10480,13 +10487,13 @@
         <v>101.96</v>
       </c>
       <c r="H171" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I171" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J171" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L171">
         <v>56.44521248842883</v>
@@ -10518,7 +10525,7 @@
     </row>
     <row r="172" spans="2:30">
       <c r="B172" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C172">
         <v>29.98</v>
@@ -10527,13 +10534,13 @@
         <v>101.96</v>
       </c>
       <c r="H172" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I172" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J172" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L172">
         <v>52.19555132795672</v>
@@ -10565,7 +10572,7 @@
     </row>
     <row r="173" spans="2:30">
       <c r="B173" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C173">
         <v>29.98</v>
@@ -10574,13 +10581,13 @@
         <v>101.96</v>
       </c>
       <c r="H173" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I173" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J173" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L173">
         <v>54.52213687530745</v>
@@ -10612,7 +10619,7 @@
     </row>
     <row r="174" spans="2:30">
       <c r="B174" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C174">
         <v>29.98</v>
@@ -10621,13 +10628,13 @@
         <v>101.96</v>
       </c>
       <c r="H174" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I174" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J174" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L174">
         <v>47.66916020061562</v>
@@ -10659,7 +10666,7 @@
     </row>
     <row r="175" spans="2:30">
       <c r="B175" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C175">
         <v>29.98</v>
@@ -10668,13 +10675,13 @@
         <v>101.96</v>
       </c>
       <c r="H175" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I175" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J175" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L175">
         <v>50.92900304070201</v>
@@ -10706,7 +10713,7 @@
     </row>
     <row r="176" spans="2:30">
       <c r="B176" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C176">
         <v>29.98</v>
@@ -10715,13 +10722,13 @@
         <v>101.96</v>
       </c>
       <c r="H176" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I176" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J176" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L176">
         <v>53.45583423204749</v>
@@ -10753,7 +10760,7 @@
     </row>
     <row r="177" spans="2:30">
       <c r="B177" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C177">
         <v>29.97</v>
@@ -10762,13 +10769,13 @@
         <v>101.96</v>
       </c>
       <c r="H177" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I177" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J177" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L177">
         <v>49.73260298528703</v>
@@ -10800,7 +10807,7 @@
     </row>
     <row r="178" spans="2:30">
       <c r="B178" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C178">
         <v>29.39</v>
@@ -10809,13 +10816,13 @@
         <v>101.96</v>
       </c>
       <c r="H178" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I178" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J178" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L178">
         <v>14.60593126453708</v>
@@ -10847,7 +10854,7 @@
     </row>
     <row r="179" spans="2:30">
       <c r="B179" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C179">
         <v>29.39</v>
@@ -10856,13 +10863,13 @@
         <v>101.96</v>
       </c>
       <c r="H179" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I179" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J179" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L179">
         <v>15.9019813933336</v>
@@ -10894,7 +10901,7 @@
     </row>
     <row r="180" spans="2:30">
       <c r="B180" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C180">
         <v>29.39</v>
@@ -10903,13 +10910,13 @@
         <v>101.96</v>
       </c>
       <c r="H180" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I180" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J180" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L180">
         <v>14.06917153020012</v>
@@ -10941,7 +10948,7 @@
     </row>
     <row r="181" spans="2:30">
       <c r="B181" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C181">
         <v>29.39</v>
@@ -10950,13 +10957,13 @@
         <v>101.96</v>
       </c>
       <c r="H181" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I181" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J181" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L181">
         <v>18.90448104651304</v>
@@ -10988,7 +10995,7 @@
     </row>
     <row r="182" spans="2:30">
       <c r="B182" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C182">
         <v>29.39</v>
@@ -10997,13 +11004,13 @@
         <v>101.96</v>
       </c>
       <c r="H182" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I182" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J182" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L182">
         <v>16.84948635618693</v>
@@ -11035,7 +11042,7 @@
     </row>
     <row r="183" spans="2:30">
       <c r="B183" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C183">
         <v>29.95</v>
@@ -11044,13 +11051,13 @@
         <v>101.96</v>
       </c>
       <c r="H183" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I183" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J183" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L183">
         <v>36.42455688920781</v>
@@ -11082,7 +11089,7 @@
     </row>
     <row r="184" spans="2:30">
       <c r="B184" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C184">
         <v>29.95</v>
@@ -11091,13 +11098,13 @@
         <v>101.96</v>
       </c>
       <c r="H184" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I184" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J184" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L184">
         <v>35.65143064107468</v>
@@ -11129,7 +11136,7 @@
     </row>
     <row r="185" spans="2:30">
       <c r="B185" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C185">
         <v>29.95</v>
@@ -11138,13 +11145,13 @@
         <v>101.96</v>
       </c>
       <c r="H185" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I185" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J185" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L185">
         <v>34.8025747362314</v>
@@ -11176,7 +11183,7 @@
     </row>
     <row r="186" spans="2:30">
       <c r="B186" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C186">
         <v>29.95</v>
@@ -11185,13 +11192,13 @@
         <v>101.96</v>
       </c>
       <c r="H186" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I186" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J186" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L186">
         <v>33.52889993282449</v>
@@ -11223,7 +11230,7 @@
     </row>
     <row r="187" spans="2:30">
       <c r="B187" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C187">
         <v>29.95</v>
@@ -11232,13 +11239,13 @@
         <v>101.96</v>
       </c>
       <c r="H187" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I187" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J187" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L187">
         <v>36.22217852178785</v>
@@ -11270,7 +11277,7 @@
     </row>
     <row r="188" spans="2:30">
       <c r="B188" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C188">
         <v>29.95</v>
@@ -11279,13 +11286,13 @@
         <v>101.96</v>
       </c>
       <c r="H188" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I188" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J188" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L188">
         <v>36.98173558027523</v>
@@ -11317,7 +11324,7 @@
     </row>
     <row r="189" spans="2:30">
       <c r="B189" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C189">
         <v>29.95</v>
@@ -11326,13 +11333,13 @@
         <v>101.96</v>
       </c>
       <c r="H189" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I189" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J189" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L189">
         <v>35.0283078096784</v>
@@ -11364,7 +11371,7 @@
     </row>
     <row r="190" spans="2:30">
       <c r="B190" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C190">
         <v>29.95</v>
@@ -11373,13 +11380,13 @@
         <v>101.96</v>
       </c>
       <c r="H190" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I190" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J190" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L190">
         <v>34.45224195894043</v>
@@ -11411,7 +11418,7 @@
     </row>
     <row r="191" spans="2:30">
       <c r="B191" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C191">
         <v>29.95</v>
@@ -11420,13 +11427,13 @@
         <v>101.96</v>
       </c>
       <c r="H191" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I191" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J191" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L191">
         <v>37.34133118348795</v>
@@ -11458,7 +11465,7 @@
     </row>
     <row r="192" spans="2:30">
       <c r="B192" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C192">
         <v>29.95</v>
@@ -11467,13 +11474,13 @@
         <v>101.96</v>
       </c>
       <c r="H192" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I192" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J192" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L192">
         <v>34.55722886372006</v>
@@ -11505,7 +11512,7 @@
     </row>
     <row r="193" spans="2:30">
       <c r="B193" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C193">
         <v>29.95</v>
@@ -11514,13 +11521,13 @@
         <v>101.96</v>
       </c>
       <c r="H193" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I193" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J193" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L193">
         <v>34.84169132984621</v>
@@ -11552,7 +11559,7 @@
     </row>
     <row r="194" spans="2:30">
       <c r="B194" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C194">
         <v>29.95</v>
@@ -11561,13 +11568,13 @@
         <v>101.96</v>
       </c>
       <c r="H194" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I194" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J194" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L194">
         <v>40.25535359595114</v>
@@ -11599,7 +11606,7 @@
     </row>
     <row r="195" spans="2:30">
       <c r="B195" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C195">
         <v>29.95</v>
@@ -11608,13 +11615,13 @@
         <v>101.96</v>
       </c>
       <c r="H195" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I195" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J195" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L195">
         <v>32.535496624289</v>
@@ -11646,7 +11653,7 @@
     </row>
     <row r="196" spans="2:30">
       <c r="B196" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C196">
         <v>29.95</v>
@@ -11655,13 +11662,13 @@
         <v>101.96</v>
       </c>
       <c r="H196" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I196" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J196" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L196">
         <v>36.55951424677289</v>
@@ -11693,7 +11700,7 @@
     </row>
     <row r="197" spans="2:30">
       <c r="B197" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C197">
         <v>29.95</v>
@@ -11702,13 +11709,13 @@
         <v>101.96</v>
       </c>
       <c r="H197" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I197" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J197" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L197">
         <v>33.08948085221236</v>
@@ -11740,7 +11747,7 @@
     </row>
     <row r="198" spans="2:30">
       <c r="B198" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C198">
         <v>29.95</v>
@@ -11749,13 +11756,13 @@
         <v>101.96</v>
       </c>
       <c r="H198" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I198" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J198" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L198">
         <v>32.31431810430986</v>
@@ -11787,7 +11794,7 @@
     </row>
     <row r="199" spans="2:30">
       <c r="B199" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C199">
         <v>29.95</v>
@@ -11796,13 +11803,13 @@
         <v>101.96</v>
       </c>
       <c r="H199" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I199" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J199" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L199">
         <v>34.13243603061409</v>
@@ -11834,7 +11841,7 @@
     </row>
     <row r="200" spans="2:30">
       <c r="B200" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C200">
         <v>29.96</v>
@@ -11843,13 +11850,13 @@
         <v>101.96</v>
       </c>
       <c r="H200" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I200" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J200" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L200">
         <v>86.21880949320132</v>
@@ -11881,7 +11888,7 @@
     </row>
     <row r="201" spans="2:30">
       <c r="B201" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C201">
         <v>29.59</v>
@@ -11890,13 +11897,13 @@
         <v>102.03</v>
       </c>
       <c r="H201" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I201" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J201" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L201">
         <v>14.40453219235653</v>
@@ -11928,7 +11935,7 @@
     </row>
     <row r="202" spans="2:30">
       <c r="B202" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C202">
         <v>29.59</v>
@@ -11937,13 +11944,13 @@
         <v>102.03</v>
       </c>
       <c r="H202" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I202" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J202" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L202">
         <v>15.22075373954788</v>
@@ -11975,7 +11982,7 @@
     </row>
     <row r="203" spans="2:30">
       <c r="B203" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C203">
         <v>29.59</v>
@@ -11984,13 +11991,13 @@
         <v>102.03</v>
       </c>
       <c r="H203" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I203" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J203" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L203">
         <v>14.13598827574029</v>
@@ -12022,7 +12029,7 @@
     </row>
     <row r="204" spans="2:30">
       <c r="B204" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C204">
         <v>29.59</v>
@@ -12031,13 +12038,13 @@
         <v>102.03</v>
       </c>
       <c r="H204" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I204" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J204" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L204">
         <v>14.8889146764632</v>
@@ -12069,7 +12076,7 @@
     </row>
     <row r="205" spans="2:30">
       <c r="B205" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C205">
         <v>29.59</v>
@@ -12078,13 +12085,13 @@
         <v>102.03</v>
       </c>
       <c r="H205" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I205" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J205" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L205">
         <v>11.3466767561168</v>
@@ -12116,7 +12123,7 @@
     </row>
     <row r="206" spans="2:30">
       <c r="B206" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C206">
         <v>29.59</v>
@@ -12125,13 +12132,13 @@
         <v>102.03</v>
       </c>
       <c r="H206" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I206" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J206" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L206">
         <v>13.70139727732138</v>
@@ -12163,7 +12170,7 @@
     </row>
     <row r="207" spans="2:30">
       <c r="B207" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C207">
         <v>29.59</v>
@@ -12172,13 +12179,13 @@
         <v>102.03</v>
       </c>
       <c r="H207" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I207" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J207" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L207">
         <v>17.39217344529752</v>
@@ -12210,7 +12217,7 @@
     </row>
     <row r="208" spans="2:30">
       <c r="B208" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C208">
         <v>29.59</v>
@@ -12219,13 +12226,13 @@
         <v>102.03</v>
       </c>
       <c r="H208" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I208" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J208" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L208">
         <v>20.07216161178604</v>
@@ -12257,7 +12264,7 @@
     </row>
     <row r="209" spans="2:30">
       <c r="B209" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C209">
         <v>29.59</v>
@@ -12266,13 +12273,13 @@
         <v>102.03</v>
       </c>
       <c r="H209" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I209" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J209" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L209">
         <v>13.6346728821199</v>
@@ -12304,7 +12311,7 @@
     </row>
     <row r="210" spans="2:30">
       <c r="B210" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C210">
         <v>29.59</v>
@@ -12313,13 +12320,13 @@
         <v>102.03</v>
       </c>
       <c r="H210" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I210" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J210" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L210">
         <v>22.79049192549948</v>
@@ -12351,7 +12358,7 @@
     </row>
     <row r="211" spans="2:30">
       <c r="B211" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C211">
         <v>29.59</v>
@@ -12360,13 +12367,13 @@
         <v>102.03</v>
       </c>
       <c r="H211" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I211" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J211" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L211">
         <v>16.31709870909099</v>
@@ -12398,7 +12405,7 @@
     </row>
     <row r="212" spans="2:30">
       <c r="B212" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C212">
         <v>29.59</v>
@@ -12407,13 +12414,13 @@
         <v>102.03</v>
       </c>
       <c r="H212" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I212" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J212" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L212">
         <v>21.00135857859604</v>
@@ -12445,7 +12452,7 @@
     </row>
     <row r="213" spans="2:30">
       <c r="B213" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C213">
         <v>29.59</v>
@@ -12454,13 +12461,13 @@
         <v>102.03</v>
       </c>
       <c r="H213" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I213" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J213" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L213">
         <v>19.00770818942219</v>
@@ -12492,7 +12499,7 @@
     </row>
     <row r="214" spans="2:30">
       <c r="B214" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C214">
         <v>29.59</v>
@@ -12501,13 +12508,13 @@
         <v>102.03</v>
       </c>
       <c r="H214" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I214" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J214" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L214">
         <v>11.68148298748257</v>
@@ -12539,7 +12546,7 @@
     </row>
     <row r="215" spans="2:30">
       <c r="B215" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C215">
         <v>29.59</v>
@@ -12548,13 +12555,13 @@
         <v>102.03</v>
       </c>
       <c r="H215" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I215" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J215" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L215">
         <v>17.62683922298473</v>
@@ -12586,7 +12593,7 @@
     </row>
     <row r="216" spans="2:30">
       <c r="B216" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C216">
         <v>29.75</v>
@@ -12595,13 +12602,13 @@
         <v>102.06</v>
       </c>
       <c r="H216" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I216" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J216" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L216">
         <v>32.74721188094824</v>
@@ -12633,7 +12640,7 @@
     </row>
     <row r="217" spans="2:30">
       <c r="B217" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C217">
         <v>29.75</v>
@@ -12642,13 +12649,13 @@
         <v>102.06</v>
       </c>
       <c r="H217" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I217" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J217" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L217">
         <v>30.93847716411966</v>
@@ -12680,7 +12687,7 @@
     </row>
     <row r="218" spans="2:30">
       <c r="B218" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C218">
         <v>29.75</v>
@@ -12689,13 +12696,13 @@
         <v>102.06</v>
       </c>
       <c r="H218" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I218" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J218" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L218">
         <v>30.8303972523081</v>
@@ -12727,7 +12734,7 @@
     </row>
     <row r="219" spans="2:30">
       <c r="B219" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C219">
         <v>29.75</v>
@@ -12736,13 +12743,13 @@
         <v>102.06</v>
       </c>
       <c r="H219" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I219" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J219" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L219">
         <v>27.29509825860648</v>
@@ -12774,7 +12781,7 @@
     </row>
     <row r="220" spans="2:30">
       <c r="B220" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C220">
         <v>29.75</v>
@@ -12783,13 +12790,13 @@
         <v>102.06</v>
       </c>
       <c r="H220" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I220" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J220" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L220">
         <v>22.51163411822341</v>
@@ -12821,7 +12828,7 @@
     </row>
     <row r="221" spans="2:30">
       <c r="B221" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C221">
         <v>29.75</v>
@@ -12830,13 +12837,13 @@
         <v>102.06</v>
       </c>
       <c r="H221" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I221" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J221" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L221">
         <v>26.63900200918288</v>
@@ -12868,7 +12875,7 @@
     </row>
     <row r="222" spans="2:30">
       <c r="B222" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C222">
         <v>29.75</v>
@@ -12877,13 +12884,13 @@
         <v>102.06</v>
       </c>
       <c r="H222" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I222" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J222" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L222">
         <v>26.30410821420157</v>
@@ -12915,7 +12922,7 @@
     </row>
     <row r="223" spans="2:30">
       <c r="B223" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C223">
         <v>29.75</v>
@@ -12924,13 +12931,13 @@
         <v>102.06</v>
       </c>
       <c r="H223" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I223" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J223" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L223">
         <v>27.81497981726448</v>
@@ -12962,7 +12969,7 @@
     </row>
     <row r="224" spans="2:30">
       <c r="B224" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C224">
         <v>29.75</v>
@@ -12971,13 +12978,13 @@
         <v>102.06</v>
       </c>
       <c r="H224" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I224" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J224" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L224">
         <v>27.63838907229883</v>
@@ -13009,7 +13016,7 @@
     </row>
     <row r="225" spans="2:30">
       <c r="B225" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C225">
         <v>29.75</v>
@@ -13018,13 +13025,13 @@
         <v>102.06</v>
       </c>
       <c r="H225" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I225" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J225" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L225">
         <v>30.28123115516652</v>
@@ -13056,7 +13063,7 @@
     </row>
     <row r="226" spans="2:30">
       <c r="B226" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C226">
         <v>29.75</v>
@@ -13065,13 +13072,13 @@
         <v>102.06</v>
       </c>
       <c r="H226" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I226" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J226" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L226">
         <v>31.02279111875065</v>
@@ -13103,7 +13110,7 @@
     </row>
     <row r="227" spans="2:30">
       <c r="B227" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C227">
         <v>29.75</v>
@@ -13112,13 +13119,13 @@
         <v>102.06</v>
       </c>
       <c r="H227" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I227" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J227" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L227">
         <v>29.75820944910912</v>
@@ -13150,7 +13157,7 @@
     </row>
     <row r="228" spans="2:30">
       <c r="B228" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C228">
         <v>29.75</v>
@@ -13159,13 +13166,13 @@
         <v>102.06</v>
       </c>
       <c r="H228" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I228" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J228" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L228">
         <v>31.61701461604629</v>
@@ -13197,7 +13204,7 @@
     </row>
     <row r="229" spans="2:30">
       <c r="B229" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C229">
         <v>29.75</v>
@@ -13206,13 +13213,13 @@
         <v>102.06</v>
       </c>
       <c r="H229" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I229" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J229" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L229">
         <v>29.68247330192829</v>
@@ -13244,7 +13251,7 @@
     </row>
     <row r="230" spans="2:30">
       <c r="B230" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C230">
         <v>29.75</v>
@@ -13253,13 +13260,13 @@
         <v>102.06</v>
       </c>
       <c r="H230" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I230" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J230" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L230">
         <v>29.11284318743828</v>
@@ -13291,7 +13298,7 @@
     </row>
     <row r="231" spans="2:30">
       <c r="B231" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C231">
         <v>29.39</v>
@@ -13300,13 +13307,13 @@
         <v>102.1</v>
       </c>
       <c r="H231" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I231" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J231" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L231">
         <v>7.714586762785332</v>
@@ -13338,7 +13345,7 @@
     </row>
     <row r="232" spans="2:30">
       <c r="B232" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C232">
         <v>29.39</v>
@@ -13347,13 +13354,13 @@
         <v>102.1</v>
       </c>
       <c r="H232" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I232" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J232" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L232">
         <v>6.834209703790383</v>
@@ -13385,7 +13392,7 @@
     </row>
     <row r="233" spans="2:30">
       <c r="B233" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C233">
         <v>29.39</v>
@@ -13394,13 +13401,13 @@
         <v>102.1</v>
       </c>
       <c r="H233" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I233" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J233" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L233">
         <v>6.939054268102471</v>
@@ -13432,7 +13439,7 @@
     </row>
     <row r="234" spans="2:30">
       <c r="B234" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C234">
         <v>29.39</v>
@@ -13441,13 +13448,13 @@
         <v>102.1</v>
       </c>
       <c r="H234" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I234" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J234" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L234">
         <v>8.476382079002827</v>
@@ -13479,7 +13486,7 @@
     </row>
     <row r="235" spans="2:30">
       <c r="B235" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C235">
         <v>29.39</v>
@@ -13488,13 +13495,13 @@
         <v>102.1</v>
       </c>
       <c r="H235" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I235" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J235" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L235">
         <v>8.844965420070789</v>
@@ -13526,7 +13533,7 @@
     </row>
     <row r="236" spans="2:30">
       <c r="B236" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C236">
         <v>29.39</v>
@@ -13535,13 +13542,13 @@
         <v>102.1</v>
       </c>
       <c r="H236" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I236" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J236" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L236">
         <v>10.90788126042658</v>
@@ -13573,7 +13580,7 @@
     </row>
     <row r="237" spans="2:30">
       <c r="B237" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C237">
         <v>29.39</v>
@@ -13582,13 +13589,13 @@
         <v>102.1</v>
       </c>
       <c r="H237" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I237" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J237" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L237">
         <v>10.92670946763253</v>
@@ -13620,7 +13627,7 @@
     </row>
     <row r="238" spans="2:30">
       <c r="B238" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C238">
         <v>29.39</v>
@@ -13629,13 +13636,13 @@
         <v>102.1</v>
       </c>
       <c r="H238" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I238" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J238" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L238">
         <v>9.824551038897068</v>
@@ -13667,7 +13674,7 @@
     </row>
     <row r="239" spans="2:30">
       <c r="B239" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C239">
         <v>29.39</v>
@@ -13676,13 +13683,13 @@
         <v>102.1</v>
       </c>
       <c r="H239" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I239" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J239" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L239">
         <v>10.26973305220762</v>
@@ -13714,7 +13721,7 @@
     </row>
     <row r="240" spans="2:30">
       <c r="B240" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C240">
         <v>29.62</v>
@@ -13723,13 +13730,13 @@
         <v>102.11</v>
       </c>
       <c r="H240" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I240" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J240" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L240">
         <v>13.03942560104074</v>
@@ -13761,7 +13768,7 @@
     </row>
     <row r="241" spans="2:30">
       <c r="B241" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C241">
         <v>29.62</v>
@@ -13770,13 +13777,13 @@
         <v>102.11</v>
       </c>
       <c r="H241" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I241" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J241" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L241">
         <v>13.32036415233393</v>
@@ -13808,7 +13815,7 @@
     </row>
     <row r="242" spans="2:30">
       <c r="B242" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C242">
         <v>29.62</v>
@@ -13817,13 +13824,13 @@
         <v>102.11</v>
       </c>
       <c r="H242" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I242" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J242" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L242">
         <v>13.47635175475282</v>
@@ -13855,7 +13862,7 @@
     </row>
     <row r="243" spans="2:30">
       <c r="B243" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C243">
         <v>29.62</v>
@@ -13864,13 +13871,13 @@
         <v>102.11</v>
       </c>
       <c r="H243" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I243" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J243" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L243">
         <v>13.19939844990029</v>
@@ -13902,7 +13909,7 @@
     </row>
     <row r="244" spans="2:30">
       <c r="B244" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C244">
         <v>29.62</v>
@@ -13911,13 +13918,13 @@
         <v>102.11</v>
       </c>
       <c r="H244" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I244" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J244" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L244">
         <v>12.99837369211979</v>
@@ -13949,7 +13956,7 @@
     </row>
     <row r="245" spans="2:30">
       <c r="B245" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C245">
         <v>29.62</v>
@@ -13958,13 +13965,13 @@
         <v>102.11</v>
       </c>
       <c r="H245" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I245" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J245" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L245">
         <v>14.54756485642743</v>
@@ -13996,7 +14003,7 @@
     </row>
     <row r="246" spans="2:30">
       <c r="B246" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C246">
         <v>29.62</v>
@@ -14005,13 +14012,13 @@
         <v>102.11</v>
       </c>
       <c r="H246" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I246" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J246" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L246">
         <v>13.61867391898239</v>
@@ -14043,7 +14050,7 @@
     </row>
     <row r="247" spans="2:30">
       <c r="B247" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C247">
         <v>29.62</v>
@@ -14052,13 +14059,13 @@
         <v>102.11</v>
       </c>
       <c r="H247" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I247" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J247" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L247">
         <v>14.09925239986907</v>
@@ -14090,7 +14097,7 @@
     </row>
     <row r="248" spans="2:30">
       <c r="B248" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C248">
         <v>29.62</v>
@@ -14099,13 +14106,13 @@
         <v>102.11</v>
       </c>
       <c r="H248" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I248" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J248" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L248">
         <v>13.05290719066591</v>
@@ -14137,7 +14144,7 @@
     </row>
     <row r="249" spans="2:30">
       <c r="B249" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C249">
         <v>29.62</v>
@@ -14146,13 +14153,13 @@
         <v>102.11</v>
       </c>
       <c r="H249" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I249" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J249" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L249">
         <v>15.22230999493526</v>
@@ -14184,7 +14191,7 @@
     </row>
     <row r="250" spans="2:30">
       <c r="B250" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C250">
         <v>29.62</v>
@@ -14193,13 +14200,13 @@
         <v>102.11</v>
       </c>
       <c r="H250" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I250" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J250" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L250">
         <v>15.01927606268011</v>
@@ -14231,7 +14238,7 @@
     </row>
     <row r="251" spans="2:30">
       <c r="B251" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C251">
         <v>29.62</v>
@@ -14240,13 +14247,13 @@
         <v>102.11</v>
       </c>
       <c r="H251" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I251" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J251" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L251">
         <v>12.56067029663772</v>
@@ -14278,7 +14285,7 @@
     </row>
     <row r="252" spans="2:30">
       <c r="B252" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C252">
         <v>29.62</v>
@@ -14287,13 +14294,13 @@
         <v>102.11</v>
       </c>
       <c r="H252" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I252" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J252" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L252">
         <v>15.3170598000188</v>
@@ -14325,7 +14332,7 @@
     </row>
     <row r="253" spans="2:30">
       <c r="B253" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C253">
         <v>29.62</v>
@@ -14334,13 +14341,13 @@
         <v>102.11</v>
       </c>
       <c r="H253" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I253" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J253" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L253">
         <v>14.64853883367337</v>
@@ -14372,7 +14379,7 @@
     </row>
     <row r="254" spans="2:30">
       <c r="B254" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C254">
         <v>29.54</v>
@@ -14381,13 +14388,13 @@
         <v>102.14</v>
       </c>
       <c r="H254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I254" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J254" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L254">
         <v>36.54636448163497</v>
@@ -14419,7 +14426,7 @@
     </row>
     <row r="255" spans="2:30">
       <c r="B255" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C255">
         <v>29.54</v>
@@ -14428,13 +14435,13 @@
         <v>102.14</v>
       </c>
       <c r="H255" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I255" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J255" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L255">
         <v>36.91116957367485</v>
@@ -14466,7 +14473,7 @@
     </row>
     <row r="256" spans="2:30">
       <c r="B256" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C256">
         <v>29.54</v>
@@ -14475,13 +14482,13 @@
         <v>102.14</v>
       </c>
       <c r="H256" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I256" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J256" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L256">
         <v>36.19966659339396</v>
@@ -14513,7 +14520,7 @@
     </row>
     <row r="257" spans="2:30">
       <c r="B257" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C257">
         <v>29.54</v>
@@ -14522,13 +14529,13 @@
         <v>102.14</v>
       </c>
       <c r="H257" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I257" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J257" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L257">
         <v>40.24115324510513</v>
@@ -14560,7 +14567,7 @@
     </row>
     <row r="258" spans="2:30">
       <c r="B258" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C258">
         <v>29.54</v>
@@ -14569,13 +14576,13 @@
         <v>102.14</v>
       </c>
       <c r="H258" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I258" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J258" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L258">
         <v>38.72279380509821</v>
@@ -14607,7 +14614,7 @@
     </row>
     <row r="259" spans="2:30">
       <c r="B259" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C259">
         <v>29.54</v>
@@ -14616,13 +14623,13 @@
         <v>102.14</v>
       </c>
       <c r="H259" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I259" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J259" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L259">
         <v>40.31533485161798</v>
@@ -14654,7 +14661,7 @@
     </row>
     <row r="260" spans="2:30">
       <c r="B260" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C260">
         <v>29.49</v>
@@ -14663,13 +14670,13 @@
         <v>102.14</v>
       </c>
       <c r="H260" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I260" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J260" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L260">
         <v>12.88040345487666</v>
@@ -14701,7 +14708,7 @@
     </row>
     <row r="261" spans="2:30">
       <c r="B261" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C261">
         <v>29.49</v>
@@ -14710,13 +14717,13 @@
         <v>102.14</v>
       </c>
       <c r="H261" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I261" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J261" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L261">
         <v>13.14417209856799</v>
@@ -14748,7 +14755,7 @@
     </row>
     <row r="262" spans="2:30">
       <c r="B262" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C262">
         <v>29.49</v>
@@ -14757,13 +14764,13 @@
         <v>102.14</v>
       </c>
       <c r="H262" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I262" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J262" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L262">
         <v>12.91474619142749</v>
@@ -14795,7 +14802,7 @@
     </row>
     <row r="263" spans="2:30">
       <c r="B263" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C263">
         <v>29.49</v>
@@ -14804,13 +14811,13 @@
         <v>102.14</v>
       </c>
       <c r="H263" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I263" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J263" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L263">
         <v>13.47757547723624</v>
@@ -14842,7 +14849,7 @@
     </row>
     <row r="264" spans="2:30">
       <c r="B264" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C264">
         <v>29.49</v>
@@ -14851,13 +14858,13 @@
         <v>102.14</v>
       </c>
       <c r="H264" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I264" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J264" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L264">
         <v>13.70696881978566</v>
@@ -14889,7 +14896,7 @@
     </row>
     <row r="265" spans="2:30">
       <c r="B265" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C265">
         <v>29.49</v>
@@ -14898,13 +14905,13 @@
         <v>102.14</v>
       </c>
       <c r="H265" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I265" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J265" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L265">
         <v>15.97676707560944</v>
@@ -14936,7 +14943,7 @@
     </row>
     <row r="266" spans="2:30">
       <c r="B266" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C266">
         <v>29.49</v>
@@ -14945,13 +14952,13 @@
         <v>102.14</v>
       </c>
       <c r="H266" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I266" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J266" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L266">
         <v>17.89603042009682</v>
@@ -14983,7 +14990,7 @@
     </row>
     <row r="267" spans="2:30">
       <c r="B267" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C267">
         <v>29.49</v>
@@ -14992,13 +14999,13 @@
         <v>102.14</v>
       </c>
       <c r="H267" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I267" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J267" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L267">
         <v>28.28281690740773</v>
@@ -15030,7 +15037,7 @@
     </row>
     <row r="268" spans="2:30">
       <c r="B268" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C268">
         <v>29.49</v>
@@ -15039,13 +15046,13 @@
         <v>102.14</v>
       </c>
       <c r="H268" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I268" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J268" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L268">
         <v>26.94461880375358</v>
@@ -15077,7 +15084,7 @@
     </row>
     <row r="269" spans="2:30">
       <c r="B269" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C269">
         <v>29.49</v>
@@ -15086,13 +15093,13 @@
         <v>102.14</v>
       </c>
       <c r="H269" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I269" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J269" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L269">
         <v>12.07341603011859</v>
@@ -15124,7 +15131,7 @@
     </row>
     <row r="270" spans="2:30">
       <c r="B270" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C270">
         <v>29.44</v>
@@ -15133,13 +15140,13 @@
         <v>102.22</v>
       </c>
       <c r="H270" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I270" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J270" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L270">
         <v>3.362111045531387</v>
@@ -15171,7 +15178,7 @@
     </row>
     <row r="271" spans="2:30">
       <c r="B271" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C271">
         <v>29.44</v>
@@ -15180,13 +15187,13 @@
         <v>102.22</v>
       </c>
       <c r="H271" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I271" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J271" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L271">
         <v>3.3178589281041</v>
@@ -15218,7 +15225,7 @@
     </row>
     <row r="272" spans="2:30">
       <c r="B272" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C272">
         <v>29.44</v>
@@ -15227,13 +15234,13 @@
         <v>102.22</v>
       </c>
       <c r="H272" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I272" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J272" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L272">
         <v>3.077803120642113</v>
@@ -15265,7 +15272,7 @@
     </row>
     <row r="273" spans="2:30">
       <c r="B273" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C273">
         <v>29.44</v>
@@ -15274,13 +15281,13 @@
         <v>102.22</v>
       </c>
       <c r="H273" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I273" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J273" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L273">
         <v>2.593011319018456</v>
@@ -15312,7 +15319,7 @@
     </row>
     <row r="274" spans="2:30">
       <c r="B274" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C274">
         <v>29.44</v>
@@ -15321,13 +15328,13 @@
         <v>102.22</v>
       </c>
       <c r="H274" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I274" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J274" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L274">
         <v>3.203398062720459</v>
@@ -15359,7 +15366,7 @@
     </row>
     <row r="275" spans="2:30">
       <c r="B275" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C275">
         <v>29.44</v>
@@ -15368,13 +15375,13 @@
         <v>102.22</v>
       </c>
       <c r="H275" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I275" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J275" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="L275">
         <v>3.052490446505272</v>
@@ -15406,7 +15413,7 @@
     </row>
     <row r="276" spans="2:30">
       <c r="B276" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C276">
         <v>29.44</v>
@@ -15415,13 +15422,13 @@
         <v>102.22</v>
       </c>
       <c r="H276" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I276" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J276" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L276">
         <v>2.667766128903645</v>
@@ -15453,7 +15460,7 @@
     </row>
     <row r="277" spans="2:30">
       <c r="B277" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C277">
         <v>29.44</v>
@@ -15462,13 +15469,13 @@
         <v>102.22</v>
       </c>
       <c r="H277" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I277" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J277" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L277">
         <v>2.653854941572961</v>
@@ -15500,7 +15507,7 @@
     </row>
     <row r="278" spans="2:30">
       <c r="B278" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C278">
         <v>29.44</v>
@@ -15509,13 +15516,13 @@
         <v>102.22</v>
       </c>
       <c r="H278" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I278" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J278" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L278">
         <v>2.694607575851763</v>
@@ -15547,7 +15554,7 @@
     </row>
     <row r="279" spans="2:30">
       <c r="B279" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C279">
         <v>29.44</v>
@@ -15556,13 +15563,13 @@
         <v>102.22</v>
       </c>
       <c r="H279" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I279" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J279" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L279">
         <v>2.647626007823968</v>
@@ -15594,7 +15601,7 @@
     </row>
     <row r="280" spans="2:30">
       <c r="B280" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C280">
         <v>29.44</v>
@@ -15603,13 +15610,13 @@
         <v>102.22</v>
       </c>
       <c r="H280" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I280" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J280" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L280">
         <v>3.537434851927873</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/after_conversion_xian_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/after_conversion_xian_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="683">
   <si>
     <t>location</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>W43</t>
+  </si>
+  <si>
+    <t>Metamorphic Rock</t>
   </si>
   <si>
     <t>10</t>
@@ -2431,7 +2434,7 @@
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" customWidth="1"/>
@@ -2558,14 +2561,17 @@
       <c r="D2">
         <v>100.25</v>
       </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L2">
         <v>21.08912739393014</v>
@@ -2605,14 +2611,17 @@
       <c r="D3">
         <v>100.25</v>
       </c>
+      <c r="F3" t="s">
+        <v>75</v>
+      </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L3">
         <v>30.17535714645276</v>
@@ -2652,14 +2661,17 @@
       <c r="D4">
         <v>100.25</v>
       </c>
+      <c r="F4" t="s">
+        <v>75</v>
+      </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L4">
         <v>23.5265234288435</v>
@@ -2699,14 +2711,17 @@
       <c r="D5">
         <v>100.29</v>
       </c>
+      <c r="F5" t="s">
+        <v>75</v>
+      </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L5">
         <v>3.800171659854208</v>
@@ -2746,14 +2761,17 @@
       <c r="D6">
         <v>100.43</v>
       </c>
+      <c r="F6" t="s">
+        <v>75</v>
+      </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L6">
         <v>9.284507592562823</v>
@@ -2787,14 +2805,17 @@
       <c r="B7" t="s">
         <v>34</v>
       </c>
+      <c r="F7" t="s">
+        <v>75</v>
+      </c>
       <c r="H7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L7">
         <v>9.156566566862834</v>
@@ -2834,14 +2855,17 @@
       <c r="D8">
         <v>100.46</v>
       </c>
+      <c r="F8" t="s">
+        <v>75</v>
+      </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J8" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L8">
         <v>43.67995747258725</v>
@@ -2881,14 +2905,17 @@
       <c r="D9">
         <v>100.46</v>
       </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
       <c r="H9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L9">
         <v>40.75096193078116</v>
@@ -2928,14 +2955,17 @@
       <c r="D10">
         <v>100.46</v>
       </c>
+      <c r="F10" t="s">
+        <v>75</v>
+      </c>
       <c r="H10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L10">
         <v>43.15379554873063</v>
@@ -2975,14 +3005,17 @@
       <c r="D11">
         <v>100.72</v>
       </c>
+      <c r="F11" t="s">
+        <v>75</v>
+      </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L11">
         <v>34.09802421490964</v>
@@ -3022,14 +3055,17 @@
       <c r="D12">
         <v>100.72</v>
       </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L12">
         <v>49.94566776598221</v>
@@ -3069,14 +3105,17 @@
       <c r="D13">
         <v>100.8</v>
       </c>
+      <c r="F13" t="s">
+        <v>75</v>
+      </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J13" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L13">
         <v>51.14694707191191</v>
@@ -3116,14 +3155,17 @@
       <c r="D14">
         <v>100.8</v>
       </c>
+      <c r="F14" t="s">
+        <v>75</v>
+      </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J14" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L14">
         <v>53.75440846080464</v>
@@ -3163,14 +3205,17 @@
       <c r="D15">
         <v>100.8</v>
       </c>
+      <c r="F15" t="s">
+        <v>75</v>
+      </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L15">
         <v>50.93398407458446</v>
@@ -3210,14 +3255,17 @@
       <c r="D16">
         <v>100.8</v>
       </c>
+      <c r="F16" t="s">
+        <v>75</v>
+      </c>
       <c r="H16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J16" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L16">
         <v>54.5028208271944</v>
@@ -3257,14 +3305,17 @@
       <c r="D17">
         <v>100.8</v>
       </c>
+      <c r="F17" t="s">
+        <v>75</v>
+      </c>
       <c r="H17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J17" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L17">
         <v>72.18358139847477</v>
@@ -3301,14 +3352,17 @@
       <c r="D18">
         <v>100.8</v>
       </c>
+      <c r="F18" t="s">
+        <v>75</v>
+      </c>
       <c r="H18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J18" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L18">
         <v>57.86291136048107</v>
@@ -3348,14 +3402,17 @@
       <c r="D19">
         <v>100.8</v>
       </c>
+      <c r="F19" t="s">
+        <v>75</v>
+      </c>
       <c r="H19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L19">
         <v>62.98254506095643</v>
@@ -3395,14 +3452,17 @@
       <c r="D20">
         <v>100.9</v>
       </c>
+      <c r="F20" t="s">
+        <v>75</v>
+      </c>
       <c r="H20" t="s">
+        <v>94</v>
+      </c>
+      <c r="I20" t="s">
         <v>93</v>
       </c>
-      <c r="I20" t="s">
-        <v>92</v>
-      </c>
       <c r="J20" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L20">
         <v>45.35822527011936</v>
@@ -3442,14 +3502,17 @@
       <c r="D21">
         <v>100.9</v>
       </c>
+      <c r="F21" t="s">
+        <v>75</v>
+      </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J21" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L21">
         <v>43.39014530096036</v>
@@ -3489,14 +3552,17 @@
       <c r="D22">
         <v>100.92</v>
       </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
       <c r="H22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J22" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L22">
         <v>46.3990218896764</v>
@@ -3536,14 +3602,17 @@
       <c r="D23">
         <v>100.92</v>
       </c>
+      <c r="F23" t="s">
+        <v>75</v>
+      </c>
       <c r="H23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J23" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L23">
         <v>54.3225280397232</v>
@@ -3583,14 +3652,17 @@
       <c r="D24">
         <v>100.92</v>
       </c>
+      <c r="F24" t="s">
+        <v>75</v>
+      </c>
       <c r="H24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I24" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J24" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L24">
         <v>57.22557557830984</v>
@@ -3630,14 +3702,17 @@
       <c r="D25">
         <v>100.92</v>
       </c>
+      <c r="F25" t="s">
+        <v>75</v>
+      </c>
       <c r="H25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I25" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J25" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L25">
         <v>48.9158630719127</v>
@@ -3677,14 +3752,17 @@
       <c r="D26">
         <v>101.01</v>
       </c>
+      <c r="F26" t="s">
+        <v>75</v>
+      </c>
       <c r="H26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J26" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L26">
         <v>44.80676537016727</v>
@@ -3724,14 +3802,17 @@
       <c r="D27">
         <v>101.01</v>
       </c>
+      <c r="F27" t="s">
+        <v>75</v>
+      </c>
       <c r="H27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J27" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L27">
         <v>46.47068321954421</v>
@@ -3771,14 +3852,17 @@
       <c r="D28">
         <v>101.01</v>
       </c>
+      <c r="F28" t="s">
+        <v>75</v>
+      </c>
       <c r="H28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I28" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J28" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L28">
         <v>46.96139688012546</v>
@@ -3818,14 +3902,17 @@
       <c r="D29">
         <v>101.02</v>
       </c>
+      <c r="F29" t="s">
+        <v>75</v>
+      </c>
       <c r="H29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I29" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L29">
         <v>49.77192785496188</v>
@@ -3865,14 +3952,17 @@
       <c r="D30">
         <v>101.08</v>
       </c>
+      <c r="F30" t="s">
+        <v>75</v>
+      </c>
       <c r="H30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J30" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L30">
         <v>24.95566663728924</v>
@@ -3912,14 +4002,17 @@
       <c r="D31">
         <v>101.08</v>
       </c>
+      <c r="F31" t="s">
+        <v>75</v>
+      </c>
       <c r="H31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I31" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J31" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L31">
         <v>24.84880023099017</v>
@@ -3959,14 +4052,17 @@
       <c r="D32">
         <v>101.08</v>
       </c>
+      <c r="F32" t="s">
+        <v>75</v>
+      </c>
       <c r="H32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J32" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L32">
         <v>24.54390391256988</v>
@@ -4006,14 +4102,17 @@
       <c r="D33">
         <v>101.1</v>
       </c>
+      <c r="F33" t="s">
+        <v>75</v>
+      </c>
       <c r="H33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L33">
         <v>48.3837744064822</v>
@@ -4053,14 +4152,17 @@
       <c r="D34">
         <v>101.1</v>
       </c>
+      <c r="F34" t="s">
+        <v>75</v>
+      </c>
       <c r="H34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J34" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L34">
         <v>50.29572292657652</v>
@@ -4100,14 +4202,17 @@
       <c r="D35">
         <v>101.1</v>
       </c>
+      <c r="F35" t="s">
+        <v>75</v>
+      </c>
       <c r="H35" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J35" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L35">
         <v>50.4336057927952</v>
@@ -4147,14 +4252,17 @@
       <c r="D36">
         <v>101.1</v>
       </c>
+      <c r="F36" t="s">
+        <v>75</v>
+      </c>
       <c r="H36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J36" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L36">
         <v>49.18214967451161</v>
@@ -4194,14 +4302,17 @@
       <c r="D37">
         <v>101.1</v>
       </c>
+      <c r="F37" t="s">
+        <v>75</v>
+      </c>
       <c r="H37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I37" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J37" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L37">
         <v>46.86202286356115</v>
@@ -4241,14 +4352,17 @@
       <c r="D38">
         <v>101.17</v>
       </c>
+      <c r="F38" t="s">
+        <v>75</v>
+      </c>
       <c r="H38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I38" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J38" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L38">
         <v>20.94581035913522</v>
@@ -4288,14 +4402,17 @@
       <c r="D39">
         <v>101.17</v>
       </c>
+      <c r="F39" t="s">
+        <v>75</v>
+      </c>
       <c r="H39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I39" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J39" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L39">
         <v>20.18934961750644</v>
@@ -4335,14 +4452,17 @@
       <c r="D40">
         <v>101.18</v>
       </c>
+      <c r="F40" t="s">
+        <v>75</v>
+      </c>
       <c r="H40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I40" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J40" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L40">
         <v>28.17387725878928</v>
@@ -4382,14 +4502,17 @@
       <c r="D41">
         <v>101.18</v>
       </c>
+      <c r="F41" t="s">
+        <v>75</v>
+      </c>
       <c r="H41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I41" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J41" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L41">
         <v>26.76027041300777</v>
@@ -4429,14 +4552,17 @@
       <c r="D42">
         <v>101.18</v>
       </c>
+      <c r="F42" t="s">
+        <v>75</v>
+      </c>
       <c r="H42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I42" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J42" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L42">
         <v>20.13137269535984</v>
@@ -4476,14 +4602,17 @@
       <c r="D43">
         <v>101.18</v>
       </c>
+      <c r="F43" t="s">
+        <v>75</v>
+      </c>
       <c r="H43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I43" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J43" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L43">
         <v>18.19704262029214</v>
@@ -4523,14 +4652,17 @@
       <c r="D44">
         <v>101.24</v>
       </c>
+      <c r="F44" t="s">
+        <v>75</v>
+      </c>
       <c r="H44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I44" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J44" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L44">
         <v>75.57117322625511</v>
@@ -4570,14 +4702,17 @@
       <c r="D45">
         <v>101.24</v>
       </c>
+      <c r="F45" t="s">
+        <v>75</v>
+      </c>
       <c r="H45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J45" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L45">
         <v>75.30040236140272</v>
@@ -4617,14 +4752,17 @@
       <c r="D46">
         <v>101.24</v>
       </c>
+      <c r="F46" t="s">
+        <v>75</v>
+      </c>
       <c r="H46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I46" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J46" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L46">
         <v>80.55946803506168</v>
@@ -4664,14 +4802,17 @@
       <c r="D47">
         <v>101.24</v>
       </c>
+      <c r="F47" t="s">
+        <v>75</v>
+      </c>
       <c r="H47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I47" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J47" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L47">
         <v>81.89838659479847</v>
@@ -4711,14 +4852,17 @@
       <c r="D48">
         <v>101.24</v>
       </c>
+      <c r="F48" t="s">
+        <v>75</v>
+      </c>
       <c r="H48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J48" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L48">
         <v>80.34621659094329</v>
@@ -4758,14 +4902,17 @@
       <c r="D49">
         <v>101.24</v>
       </c>
+      <c r="F49" t="s">
+        <v>75</v>
+      </c>
       <c r="H49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I49" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J49" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L49">
         <v>75.19674051325606</v>
@@ -4805,14 +4952,17 @@
       <c r="D50">
         <v>101.24</v>
       </c>
+      <c r="F50" t="s">
+        <v>75</v>
+      </c>
       <c r="H50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I50" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J50" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L50">
         <v>23.5189138980576</v>
@@ -4852,14 +5002,17 @@
       <c r="D51">
         <v>101.24</v>
       </c>
+      <c r="F51" t="s">
+        <v>75</v>
+      </c>
       <c r="H51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I51" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J51" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L51">
         <v>21.63620190903845</v>
@@ -4899,14 +5052,17 @@
       <c r="D52">
         <v>101.24</v>
       </c>
+      <c r="F52" t="s">
+        <v>75</v>
+      </c>
       <c r="H52" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I52" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J52" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L52">
         <v>21.0468944762325</v>
@@ -4946,14 +5102,17 @@
       <c r="D53">
         <v>101.24</v>
       </c>
+      <c r="F53" t="s">
+        <v>75</v>
+      </c>
       <c r="H53" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I53" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J53" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L53">
         <v>20.73729514742257</v>
@@ -4993,14 +5152,17 @@
       <c r="D54">
         <v>101.24</v>
       </c>
+      <c r="F54" t="s">
+        <v>75</v>
+      </c>
       <c r="H54" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I54" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J54" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L54">
         <v>23.11448821824018</v>
@@ -5040,14 +5202,17 @@
       <c r="D55">
         <v>101.24</v>
       </c>
+      <c r="F55" t="s">
+        <v>75</v>
+      </c>
       <c r="H55" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I55" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J55" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L55">
         <v>18.76707898009298</v>
@@ -5087,14 +5252,17 @@
       <c r="D56">
         <v>101.24</v>
       </c>
+      <c r="F56" t="s">
+        <v>75</v>
+      </c>
       <c r="H56" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J56" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L56">
         <v>25.53348354146977</v>
@@ -5134,14 +5302,17 @@
       <c r="D57">
         <v>101.24</v>
       </c>
+      <c r="F57" t="s">
+        <v>75</v>
+      </c>
       <c r="H57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I57" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J57" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L57">
         <v>28.53373201124357</v>
@@ -5181,14 +5352,17 @@
       <c r="D58">
         <v>101.24</v>
       </c>
+      <c r="F58" t="s">
+        <v>75</v>
+      </c>
       <c r="H58" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I58" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J58" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L58">
         <v>27.9385085597912</v>
@@ -5228,14 +5402,17 @@
       <c r="D59">
         <v>101.24</v>
       </c>
+      <c r="F59" t="s">
+        <v>75</v>
+      </c>
       <c r="H59" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J59" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L59">
         <v>29.30694801309367</v>
@@ -5275,14 +5452,17 @@
       <c r="D60">
         <v>101.24</v>
       </c>
+      <c r="F60" t="s">
+        <v>75</v>
+      </c>
       <c r="H60" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J60" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L60">
         <v>27.0973519169432</v>
@@ -5322,14 +5502,17 @@
       <c r="D61">
         <v>101.24</v>
       </c>
+      <c r="F61" t="s">
+        <v>75</v>
+      </c>
       <c r="H61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J61" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L61">
         <v>28.18672603981994</v>
@@ -5369,14 +5552,17 @@
       <c r="D62">
         <v>101.24</v>
       </c>
+      <c r="F62" t="s">
+        <v>75</v>
+      </c>
       <c r="H62" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J62" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L62">
         <v>27.90429096702293</v>
@@ -5416,14 +5602,17 @@
       <c r="D63">
         <v>101.24</v>
       </c>
+      <c r="F63" t="s">
+        <v>75</v>
+      </c>
       <c r="H63" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J63" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L63">
         <v>27.11962028598113</v>
@@ -5463,14 +5652,17 @@
       <c r="D64">
         <v>101.24</v>
       </c>
+      <c r="F64" t="s">
+        <v>75</v>
+      </c>
       <c r="H64" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J64" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L64">
         <v>26.8331093354449</v>
@@ -5510,14 +5702,17 @@
       <c r="D65">
         <v>101.24</v>
       </c>
+      <c r="F65" t="s">
+        <v>75</v>
+      </c>
       <c r="H65" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J65" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L65">
         <v>26.85381716780866</v>
@@ -5557,14 +5752,17 @@
       <c r="D66">
         <v>101.24</v>
       </c>
+      <c r="F66" t="s">
+        <v>75</v>
+      </c>
       <c r="H66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J66" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L66">
         <v>19.86669245036554</v>
@@ -5604,14 +5802,17 @@
       <c r="D67">
         <v>101.24</v>
       </c>
+      <c r="F67" t="s">
+        <v>75</v>
+      </c>
       <c r="H67" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J67" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L67">
         <v>28.329894269076</v>
@@ -5651,14 +5852,17 @@
       <c r="D68">
         <v>101.24</v>
       </c>
+      <c r="F68" t="s">
+        <v>75</v>
+      </c>
       <c r="H68" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J68" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L68">
         <v>32.3108392039136</v>
@@ -5698,14 +5902,17 @@
       <c r="D69">
         <v>101.24</v>
       </c>
+      <c r="F69" t="s">
+        <v>75</v>
+      </c>
       <c r="H69" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I69" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J69" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L69">
         <v>23.04590686925087</v>
@@ -5745,14 +5952,17 @@
       <c r="D70">
         <v>101.24</v>
       </c>
+      <c r="F70" t="s">
+        <v>75</v>
+      </c>
       <c r="H70" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J70" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L70">
         <v>31.79981769246117</v>
@@ -5792,14 +6002,17 @@
       <c r="D71">
         <v>101.24</v>
       </c>
+      <c r="F71" t="s">
+        <v>75</v>
+      </c>
       <c r="H71" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J71" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L71">
         <v>29.22244276946949</v>
@@ -5839,14 +6052,17 @@
       <c r="D72">
         <v>101.29</v>
       </c>
+      <c r="F72" t="s">
+        <v>75</v>
+      </c>
       <c r="H72" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J72" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L72">
         <v>17.8635493199819</v>
@@ -5886,14 +6102,17 @@
       <c r="D73">
         <v>101.29</v>
       </c>
+      <c r="F73" t="s">
+        <v>75</v>
+      </c>
       <c r="H73" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J73" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L73">
         <v>18.14970120813148</v>
@@ -5933,14 +6152,17 @@
       <c r="D74">
         <v>101.29</v>
       </c>
+      <c r="F74" t="s">
+        <v>75</v>
+      </c>
       <c r="H74" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J74" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L74">
         <v>24.81478423606316</v>
@@ -5980,14 +6202,17 @@
       <c r="D75">
         <v>101.29</v>
       </c>
+      <c r="F75" t="s">
+        <v>75</v>
+      </c>
       <c r="H75" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I75" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J75" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L75">
         <v>24.13106836583459</v>
@@ -6027,14 +6252,17 @@
       <c r="D76">
         <v>101.29</v>
       </c>
+      <c r="F76" t="s">
+        <v>75</v>
+      </c>
       <c r="H76" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I76" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J76" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L76">
         <v>25.0251369848728</v>
@@ -6074,14 +6302,17 @@
       <c r="D77">
         <v>101.4</v>
       </c>
+      <c r="F77" t="s">
+        <v>75</v>
+      </c>
       <c r="H77" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I77" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J77" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L77">
         <v>25.09750910627882</v>
@@ -6121,14 +6352,17 @@
       <c r="D78">
         <v>101.53</v>
       </c>
+      <c r="F78" t="s">
+        <v>75</v>
+      </c>
       <c r="H78" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I78" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J78" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L78">
         <v>25.81480632619078</v>
@@ -6168,14 +6402,17 @@
       <c r="D79">
         <v>101.53</v>
       </c>
+      <c r="F79" t="s">
+        <v>75</v>
+      </c>
       <c r="H79" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J79" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L79">
         <v>29.82416625277004</v>
@@ -6215,14 +6452,17 @@
       <c r="D80">
         <v>101.53</v>
       </c>
+      <c r="F80" t="s">
+        <v>75</v>
+      </c>
       <c r="H80" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I80" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J80" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L80">
         <v>22.81208914193508</v>
@@ -6262,14 +6502,17 @@
       <c r="D81">
         <v>101.62</v>
       </c>
+      <c r="F81" t="s">
+        <v>75</v>
+      </c>
       <c r="H81" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I81" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J81" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L81">
         <v>45.96861249873792</v>
@@ -6309,14 +6552,17 @@
       <c r="D82">
         <v>101.62</v>
       </c>
+      <c r="F82" t="s">
+        <v>75</v>
+      </c>
       <c r="H82" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I82" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J82" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L82">
         <v>44.32547214922285</v>
@@ -6356,14 +6602,17 @@
       <c r="D83">
         <v>101.62</v>
       </c>
+      <c r="F83" t="s">
+        <v>75</v>
+      </c>
       <c r="H83" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I83" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J83" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L83">
         <v>48.09923536518973</v>
@@ -6403,14 +6652,17 @@
       <c r="D84">
         <v>101.62</v>
       </c>
+      <c r="F84" t="s">
+        <v>75</v>
+      </c>
       <c r="H84" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I84" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J84" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L84">
         <v>64.72470340259186</v>
@@ -6450,14 +6702,17 @@
       <c r="D85">
         <v>101.62</v>
       </c>
+      <c r="F85" t="s">
+        <v>75</v>
+      </c>
       <c r="H85" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I85" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J85" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L85">
         <v>46.45969263668794</v>
@@ -6497,14 +6752,17 @@
       <c r="D86">
         <v>101.62</v>
       </c>
+      <c r="F86" t="s">
+        <v>75</v>
+      </c>
       <c r="H86" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I86" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J86" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L86">
         <v>50.14575301081393</v>
@@ -6544,14 +6802,17 @@
       <c r="D87">
         <v>101.62</v>
       </c>
+      <c r="F87" t="s">
+        <v>75</v>
+      </c>
       <c r="H87" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J87" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L87">
         <v>49.94079672434388</v>
@@ -6591,14 +6852,17 @@
       <c r="D88">
         <v>101.62</v>
       </c>
+      <c r="F88" t="s">
+        <v>75</v>
+      </c>
       <c r="H88" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I88" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J88" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L88">
         <v>52.01871336357467</v>
@@ -6638,14 +6902,17 @@
       <c r="D89">
         <v>101.62</v>
       </c>
+      <c r="F89" t="s">
+        <v>75</v>
+      </c>
       <c r="H89" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I89" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J89" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L89">
         <v>50.64903072945874</v>
@@ -6685,14 +6952,17 @@
       <c r="D90">
         <v>101.62</v>
       </c>
+      <c r="F90" t="s">
+        <v>75</v>
+      </c>
       <c r="H90" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I90" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J90" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L90">
         <v>46.71018124316134</v>
@@ -6732,14 +7002,17 @@
       <c r="D91">
         <v>101.62</v>
       </c>
+      <c r="F91" t="s">
+        <v>75</v>
+      </c>
       <c r="H91" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I91" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J91" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L91">
         <v>48.85167546641829</v>
@@ -6779,14 +7052,17 @@
       <c r="D92">
         <v>101.62</v>
       </c>
+      <c r="F92" t="s">
+        <v>75</v>
+      </c>
       <c r="H92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I92" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J92" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L92">
         <v>53.84898981334889</v>
@@ -6826,14 +7102,17 @@
       <c r="D93">
         <v>101.62</v>
       </c>
+      <c r="F93" t="s">
+        <v>75</v>
+      </c>
       <c r="H93" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I93" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J93" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L93">
         <v>30.02882038022353</v>
@@ -6873,14 +7152,17 @@
       <c r="D94">
         <v>101.62</v>
       </c>
+      <c r="F94" t="s">
+        <v>75</v>
+      </c>
       <c r="H94" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I94" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J94" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L94">
         <v>27.75405170611547</v>
@@ -6920,14 +7202,17 @@
       <c r="D95">
         <v>101.62</v>
       </c>
+      <c r="F95" t="s">
+        <v>75</v>
+      </c>
       <c r="H95" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I95" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J95" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L95">
         <v>28.42240053404458</v>
@@ -6967,14 +7252,17 @@
       <c r="D96">
         <v>101.62</v>
       </c>
+      <c r="F96" t="s">
+        <v>75</v>
+      </c>
       <c r="H96" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I96" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J96" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L96">
         <v>28.48982609057824</v>
@@ -7014,14 +7302,17 @@
       <c r="D97">
         <v>101.62</v>
       </c>
+      <c r="F97" t="s">
+        <v>75</v>
+      </c>
       <c r="H97" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I97" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J97" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L97">
         <v>26.43934516635763</v>
@@ -7061,14 +7352,17 @@
       <c r="D98">
         <v>101.62</v>
       </c>
+      <c r="F98" t="s">
+        <v>75</v>
+      </c>
       <c r="H98" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I98" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J98" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L98">
         <v>26.68120899788228</v>
@@ -7108,14 +7402,17 @@
       <c r="D99">
         <v>101.84</v>
       </c>
+      <c r="F99" t="s">
+        <v>75</v>
+      </c>
       <c r="H99" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I99" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J99" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L99">
         <v>19.94011618903403</v>
@@ -7155,14 +7452,17 @@
       <c r="D100">
         <v>101.84</v>
       </c>
+      <c r="F100" t="s">
+        <v>75</v>
+      </c>
       <c r="H100" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I100" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J100" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L100">
         <v>19.91890457973786</v>
@@ -7202,14 +7502,17 @@
       <c r="D101">
         <v>101.84</v>
       </c>
+      <c r="F101" t="s">
+        <v>75</v>
+      </c>
       <c r="H101" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I101" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J101" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L101">
         <v>26.69533811770494</v>
@@ -7249,14 +7552,17 @@
       <c r="D102">
         <v>101.84</v>
       </c>
+      <c r="F102" t="s">
+        <v>75</v>
+      </c>
       <c r="H102" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I102" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J102" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L102">
         <v>22.10911744057313</v>
@@ -7296,14 +7602,17 @@
       <c r="D103">
         <v>101.86</v>
       </c>
+      <c r="F103" t="s">
+        <v>75</v>
+      </c>
       <c r="H103" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I103" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J103" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L103">
         <v>15.37468474539939</v>
@@ -7343,14 +7652,17 @@
       <c r="D104">
         <v>101.86</v>
       </c>
+      <c r="F104" t="s">
+        <v>75</v>
+      </c>
       <c r="H104" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I104" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J104" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L104">
         <v>15.77542948217157</v>
@@ -7390,14 +7702,17 @@
       <c r="D105">
         <v>101.86</v>
       </c>
+      <c r="F105" t="s">
+        <v>75</v>
+      </c>
       <c r="H105" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I105" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J105" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L105">
         <v>15.324651072666</v>
@@ -7437,14 +7752,17 @@
       <c r="D106">
         <v>101.86</v>
       </c>
+      <c r="F106" t="s">
+        <v>75</v>
+      </c>
       <c r="H106" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I106" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J106" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L106">
         <v>14.72650366224622</v>
@@ -7484,14 +7802,17 @@
       <c r="D107">
         <v>101.86</v>
       </c>
+      <c r="F107" t="s">
+        <v>75</v>
+      </c>
       <c r="H107" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I107" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J107" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L107">
         <v>17.05837829938186</v>
@@ -7531,14 +7852,17 @@
       <c r="D108">
         <v>101.86</v>
       </c>
+      <c r="F108" t="s">
+        <v>75</v>
+      </c>
       <c r="H108" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I108" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J108" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L108">
         <v>17.24110005926685</v>
@@ -7578,14 +7902,17 @@
       <c r="D109">
         <v>101.86</v>
       </c>
+      <c r="F109" t="s">
+        <v>75</v>
+      </c>
       <c r="H109" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I109" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J109" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L109">
         <v>20.40773391211248</v>
@@ -7625,14 +7952,17 @@
       <c r="D110">
         <v>101.86</v>
       </c>
+      <c r="F110" t="s">
+        <v>75</v>
+      </c>
       <c r="H110" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I110" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J110" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L110">
         <v>15.89232627543878</v>
@@ -7669,14 +7999,17 @@
       <c r="D111">
         <v>101.86</v>
       </c>
+      <c r="F111" t="s">
+        <v>75</v>
+      </c>
       <c r="H111" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I111" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J111" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L111">
         <v>19.88592875771332</v>
@@ -7713,14 +8046,17 @@
       <c r="D112">
         <v>101.86</v>
       </c>
+      <c r="F112" t="s">
+        <v>75</v>
+      </c>
       <c r="H112" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I112" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J112" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L112">
         <v>17.89329009996987</v>
@@ -7760,14 +8096,17 @@
       <c r="D113">
         <v>101.86</v>
       </c>
+      <c r="F113" t="s">
+        <v>75</v>
+      </c>
       <c r="H113" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I113" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J113" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L113">
         <v>14.54303389227583</v>
@@ -7807,14 +8146,17 @@
       <c r="D114">
         <v>101.86</v>
       </c>
+      <c r="F114" t="s">
+        <v>75</v>
+      </c>
       <c r="H114" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I114" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J114" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L114">
         <v>13.83545767169392</v>
@@ -7854,14 +8196,17 @@
       <c r="D115">
         <v>101.86</v>
       </c>
+      <c r="F115" t="s">
+        <v>75</v>
+      </c>
       <c r="H115" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I115" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J115" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L115">
         <v>13.68584320311183</v>
@@ -7901,14 +8246,17 @@
       <c r="D116">
         <v>101.86</v>
       </c>
+      <c r="F116" t="s">
+        <v>75</v>
+      </c>
       <c r="H116" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I116" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J116" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L116">
         <v>12.45591353194765</v>
@@ -7948,14 +8296,17 @@
       <c r="D117">
         <v>101.86</v>
       </c>
+      <c r="F117" t="s">
+        <v>75</v>
+      </c>
       <c r="H117" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I117" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J117" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L117">
         <v>11.91756507055086</v>
@@ -7995,14 +8346,17 @@
       <c r="D118">
         <v>101.86</v>
       </c>
+      <c r="F118" t="s">
+        <v>75</v>
+      </c>
       <c r="H118" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I118" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J118" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L118">
         <v>11.95563513025457</v>
@@ -8042,14 +8396,17 @@
       <c r="D119">
         <v>101.87</v>
       </c>
+      <c r="F119" t="s">
+        <v>75</v>
+      </c>
       <c r="H119" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I119" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J119" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L119">
         <v>31.43017399141223</v>
@@ -8089,14 +8446,17 @@
       <c r="D120">
         <v>101.87</v>
       </c>
+      <c r="F120" t="s">
+        <v>75</v>
+      </c>
       <c r="H120" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I120" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J120" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L120">
         <v>31.91622050186521</v>
@@ -8136,14 +8496,17 @@
       <c r="D121">
         <v>101.87</v>
       </c>
+      <c r="F121" t="s">
+        <v>75</v>
+      </c>
       <c r="H121" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I121" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J121" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L121">
         <v>30.58032625066713</v>
@@ -8183,14 +8546,17 @@
       <c r="D122">
         <v>101.87</v>
       </c>
+      <c r="F122" t="s">
+        <v>75</v>
+      </c>
       <c r="H122" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I122" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J122" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L122">
         <v>31.56037030341515</v>
@@ -8230,14 +8596,17 @@
       <c r="D123">
         <v>101.87</v>
       </c>
+      <c r="F123" t="s">
+        <v>75</v>
+      </c>
       <c r="H123" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I123" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J123" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L123">
         <v>31.39232432341603</v>
@@ -8277,14 +8646,17 @@
       <c r="D124">
         <v>101.87</v>
       </c>
+      <c r="F124" t="s">
+        <v>75</v>
+      </c>
       <c r="H124" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I124" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J124" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L124">
         <v>34.80167828725119</v>
@@ -8324,14 +8696,17 @@
       <c r="D125">
         <v>101.87</v>
       </c>
+      <c r="F125" t="s">
+        <v>75</v>
+      </c>
       <c r="H125" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I125" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J125" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L125">
         <v>33.57288310214656</v>
@@ -8371,14 +8746,17 @@
       <c r="D126">
         <v>101.87</v>
       </c>
+      <c r="F126" t="s">
+        <v>75</v>
+      </c>
       <c r="H126" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I126" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J126" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L126">
         <v>19.50268381687432</v>
@@ -8418,14 +8796,17 @@
       <c r="D127">
         <v>101.87</v>
       </c>
+      <c r="F127" t="s">
+        <v>75</v>
+      </c>
       <c r="H127" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I127" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J127" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L127">
         <v>14.13379194238786</v>
@@ -8465,14 +8846,17 @@
       <c r="D128">
         <v>101.87</v>
       </c>
+      <c r="F128" t="s">
+        <v>75</v>
+      </c>
       <c r="H128" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I128" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J128" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L128">
         <v>14.86104959320223</v>
@@ -8512,14 +8896,17 @@
       <c r="D129">
         <v>101.87</v>
       </c>
+      <c r="F129" t="s">
+        <v>75</v>
+      </c>
       <c r="H129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I129" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J129" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L129">
         <v>16.36581357255476</v>
@@ -8559,14 +8946,17 @@
       <c r="D130">
         <v>101.87</v>
       </c>
+      <c r="F130" t="s">
+        <v>75</v>
+      </c>
       <c r="H130" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I130" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J130" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L130">
         <v>16.00363576596058</v>
@@ -8606,14 +8996,17 @@
       <c r="D131">
         <v>101.87</v>
       </c>
+      <c r="F131" t="s">
+        <v>75</v>
+      </c>
       <c r="H131" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I131" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J131" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L131">
         <v>15.29552520276536</v>
@@ -8653,14 +9046,17 @@
       <c r="D132">
         <v>101.87</v>
       </c>
+      <c r="F132" t="s">
+        <v>75</v>
+      </c>
       <c r="H132" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I132" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J132" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L132">
         <v>14.71565146556761</v>
@@ -8700,14 +9096,17 @@
       <c r="D133">
         <v>101.88</v>
       </c>
+      <c r="F133" t="s">
+        <v>75</v>
+      </c>
       <c r="H133" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I133" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J133" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L133">
         <v>38.57739178662635</v>
@@ -8747,14 +9146,17 @@
       <c r="D134">
         <v>101.88</v>
       </c>
+      <c r="F134" t="s">
+        <v>75</v>
+      </c>
       <c r="H134" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I134" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J134" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L134">
         <v>43.14857177812642</v>
@@ -8794,14 +9196,17 @@
       <c r="D135">
         <v>101.88</v>
       </c>
+      <c r="F135" t="s">
+        <v>75</v>
+      </c>
       <c r="H135" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I135" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J135" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L135">
         <v>35.89813581589569</v>
@@ -8841,14 +9246,17 @@
       <c r="D136">
         <v>101.88</v>
       </c>
+      <c r="F136" t="s">
+        <v>75</v>
+      </c>
       <c r="H136" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I136" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J136" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L136">
         <v>42.29939734360386</v>
@@ -8888,14 +9296,17 @@
       <c r="D137">
         <v>101.88</v>
       </c>
+      <c r="F137" t="s">
+        <v>75</v>
+      </c>
       <c r="H137" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I137" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J137" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L137">
         <v>34.97558353986742</v>
@@ -8935,14 +9346,17 @@
       <c r="D138">
         <v>101.88</v>
       </c>
+      <c r="F138" t="s">
+        <v>75</v>
+      </c>
       <c r="H138" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I138" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J138" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L138">
         <v>35.20488780920999</v>
@@ -8982,14 +9396,17 @@
       <c r="D139">
         <v>101.88</v>
       </c>
+      <c r="F139" t="s">
+        <v>75</v>
+      </c>
       <c r="H139" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I139" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J139" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L139">
         <v>36.94026931577904</v>
@@ -9029,14 +9446,17 @@
       <c r="D140">
         <v>101.88</v>
       </c>
+      <c r="F140" t="s">
+        <v>75</v>
+      </c>
       <c r="H140" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I140" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J140" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L140">
         <v>36.72433380528662</v>
@@ -9076,14 +9496,17 @@
       <c r="D141">
         <v>101.88</v>
       </c>
+      <c r="F141" t="s">
+        <v>75</v>
+      </c>
       <c r="H141" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I141" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J141" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L141">
         <v>42.43279652002134</v>
@@ -9123,14 +9546,17 @@
       <c r="D142">
         <v>101.88</v>
       </c>
+      <c r="F142" t="s">
+        <v>75</v>
+      </c>
       <c r="H142" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I142" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J142" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L142">
         <v>35.14699980791524</v>
@@ -9170,14 +9596,17 @@
       <c r="D143">
         <v>101.95</v>
       </c>
+      <c r="F143" t="s">
+        <v>75</v>
+      </c>
       <c r="H143" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I143" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J143" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L143">
         <v>19.21331012207732</v>
@@ -9217,14 +9646,17 @@
       <c r="D144">
         <v>101.95</v>
       </c>
+      <c r="F144" t="s">
+        <v>75</v>
+      </c>
       <c r="H144" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I144" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J144" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L144">
         <v>20.47218400300838</v>
@@ -9264,14 +9696,17 @@
       <c r="D145">
         <v>101.95</v>
       </c>
+      <c r="F145" t="s">
+        <v>75</v>
+      </c>
       <c r="H145" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I145" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J145" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L145">
         <v>20.47261199020694</v>
@@ -9311,14 +9746,17 @@
       <c r="D146">
         <v>101.95</v>
       </c>
+      <c r="F146" t="s">
+        <v>75</v>
+      </c>
       <c r="H146" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I146" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J146" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L146">
         <v>20.85292113558878</v>
@@ -9358,14 +9796,17 @@
       <c r="D147">
         <v>101.95</v>
       </c>
+      <c r="F147" t="s">
+        <v>75</v>
+      </c>
       <c r="H147" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I147" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J147" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L147">
         <v>20.6698662483309</v>
@@ -9405,14 +9846,17 @@
       <c r="D148">
         <v>101.95</v>
       </c>
+      <c r="F148" t="s">
+        <v>75</v>
+      </c>
       <c r="H148" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I148" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J148" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L148">
         <v>16.81169943740878</v>
@@ -9452,14 +9896,17 @@
       <c r="D149">
         <v>101.95</v>
       </c>
+      <c r="F149" t="s">
+        <v>75</v>
+      </c>
       <c r="H149" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I149" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J149" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L149">
         <v>24.58016645722712</v>
@@ -9499,14 +9946,17 @@
       <c r="D150">
         <v>101.95</v>
       </c>
+      <c r="F150" t="s">
+        <v>75</v>
+      </c>
       <c r="H150" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I150" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J150" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L150">
         <v>26.2651347292516</v>
@@ -9546,14 +9996,17 @@
       <c r="D151">
         <v>101.95</v>
       </c>
+      <c r="F151" t="s">
+        <v>75</v>
+      </c>
       <c r="H151" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I151" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J151" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L151">
         <v>25.63945761782982</v>
@@ -9593,14 +10046,17 @@
       <c r="D152">
         <v>101.95</v>
       </c>
+      <c r="F152" t="s">
+        <v>75</v>
+      </c>
       <c r="H152" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I152" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J152" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L152">
         <v>24.871581113323</v>
@@ -9640,14 +10096,17 @@
       <c r="D153">
         <v>101.95</v>
       </c>
+      <c r="F153" t="s">
+        <v>75</v>
+      </c>
       <c r="H153" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I153" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J153" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L153">
         <v>31.48348317121073</v>
@@ -9687,14 +10146,17 @@
       <c r="D154">
         <v>101.95</v>
       </c>
+      <c r="F154" t="s">
+        <v>75</v>
+      </c>
       <c r="H154" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I154" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J154" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L154">
         <v>35.30311445726263</v>
@@ -9734,14 +10196,17 @@
       <c r="D155">
         <v>101.95</v>
       </c>
+      <c r="F155" t="s">
+        <v>75</v>
+      </c>
       <c r="H155" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I155" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J155" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L155">
         <v>34.61896775627811</v>
@@ -9781,14 +10246,17 @@
       <c r="D156">
         <v>101.95</v>
       </c>
+      <c r="F156" t="s">
+        <v>75</v>
+      </c>
       <c r="H156" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I156" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J156" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L156">
         <v>35.07729219870466</v>
@@ -9828,14 +10296,17 @@
       <c r="D157">
         <v>101.95</v>
       </c>
+      <c r="F157" t="s">
+        <v>75</v>
+      </c>
       <c r="H157" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I157" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J157" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L157">
         <v>32.02940883478603</v>
@@ -9875,14 +10346,17 @@
       <c r="D158">
         <v>101.95</v>
       </c>
+      <c r="F158" t="s">
+        <v>75</v>
+      </c>
       <c r="H158" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I158" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J158" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L158">
         <v>31.25435801743152</v>
@@ -9922,14 +10396,17 @@
       <c r="D159">
         <v>101.95</v>
       </c>
+      <c r="F159" t="s">
+        <v>75</v>
+      </c>
       <c r="H159" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I159" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J159" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L159">
         <v>34.74057152859355</v>
@@ -9969,14 +10446,17 @@
       <c r="D160">
         <v>101.96</v>
       </c>
+      <c r="F160" t="s">
+        <v>75</v>
+      </c>
       <c r="H160" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I160" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J160" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L160">
         <v>51.25714951000029</v>
@@ -10016,14 +10496,17 @@
       <c r="D161">
         <v>101.96</v>
       </c>
+      <c r="F161" t="s">
+        <v>75</v>
+      </c>
       <c r="H161" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I161" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J161" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L161">
         <v>52.26794372431828</v>
@@ -10063,14 +10546,17 @@
       <c r="D162">
         <v>101.96</v>
       </c>
+      <c r="F162" t="s">
+        <v>75</v>
+      </c>
       <c r="H162" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I162" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J162" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L162">
         <v>51.15838844159588</v>
@@ -10110,14 +10596,17 @@
       <c r="D163">
         <v>101.96</v>
       </c>
+      <c r="F163" t="s">
+        <v>75</v>
+      </c>
       <c r="H163" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I163" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J163" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L163">
         <v>51.87120090395762</v>
@@ -10157,14 +10646,17 @@
       <c r="D164">
         <v>101.96</v>
       </c>
+      <c r="F164" t="s">
+        <v>75</v>
+      </c>
       <c r="H164" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I164" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J164" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L164">
         <v>49.33417311210406</v>
@@ -10204,14 +10696,17 @@
       <c r="D165">
         <v>101.96</v>
       </c>
+      <c r="F165" t="s">
+        <v>75</v>
+      </c>
       <c r="H165" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I165" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J165" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L165">
         <v>53.26960565338417</v>
@@ -10251,14 +10746,17 @@
       <c r="D166">
         <v>101.96</v>
       </c>
+      <c r="F166" t="s">
+        <v>75</v>
+      </c>
       <c r="H166" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I166" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J166" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L166">
         <v>56.27597677482076</v>
@@ -10298,14 +10796,17 @@
       <c r="D167">
         <v>101.96</v>
       </c>
+      <c r="F167" t="s">
+        <v>75</v>
+      </c>
       <c r="H167" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I167" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J167" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L167">
         <v>53.55576121341085</v>
@@ -10345,14 +10846,17 @@
       <c r="D168">
         <v>101.96</v>
       </c>
+      <c r="F168" t="s">
+        <v>75</v>
+      </c>
       <c r="H168" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I168" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J168" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L168">
         <v>53.93662923031994</v>
@@ -10392,14 +10896,17 @@
       <c r="D169">
         <v>101.96</v>
       </c>
+      <c r="F169" t="s">
+        <v>75</v>
+      </c>
       <c r="H169" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I169" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J169" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L169">
         <v>51.24279277927307</v>
@@ -10439,14 +10946,17 @@
       <c r="D170">
         <v>101.96</v>
       </c>
+      <c r="F170" t="s">
+        <v>75</v>
+      </c>
       <c r="H170" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I170" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J170" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L170">
         <v>53.19231091790983</v>
@@ -10486,14 +10996,17 @@
       <c r="D171">
         <v>101.96</v>
       </c>
+      <c r="F171" t="s">
+        <v>75</v>
+      </c>
       <c r="H171" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I171" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J171" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L171">
         <v>56.44521248842883</v>
@@ -10533,14 +11046,17 @@
       <c r="D172">
         <v>101.96</v>
       </c>
+      <c r="F172" t="s">
+        <v>75</v>
+      </c>
       <c r="H172" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I172" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J172" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L172">
         <v>52.19555132795672</v>
@@ -10580,14 +11096,17 @@
       <c r="D173">
         <v>101.96</v>
       </c>
+      <c r="F173" t="s">
+        <v>75</v>
+      </c>
       <c r="H173" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I173" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J173" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L173">
         <v>54.52213687530745</v>
@@ -10627,14 +11146,17 @@
       <c r="D174">
         <v>101.96</v>
       </c>
+      <c r="F174" t="s">
+        <v>75</v>
+      </c>
       <c r="H174" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I174" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J174" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L174">
         <v>47.66916020061562</v>
@@ -10674,14 +11196,17 @@
       <c r="D175">
         <v>101.96</v>
       </c>
+      <c r="F175" t="s">
+        <v>75</v>
+      </c>
       <c r="H175" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I175" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J175" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L175">
         <v>50.92900304070201</v>
@@ -10721,14 +11246,17 @@
       <c r="D176">
         <v>101.96</v>
       </c>
+      <c r="F176" t="s">
+        <v>75</v>
+      </c>
       <c r="H176" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I176" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J176" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L176">
         <v>53.45583423204749</v>
@@ -10768,14 +11296,17 @@
       <c r="D177">
         <v>101.96</v>
       </c>
+      <c r="F177" t="s">
+        <v>75</v>
+      </c>
       <c r="H177" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I177" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J177" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L177">
         <v>49.73260298528703</v>
@@ -10815,14 +11346,17 @@
       <c r="D178">
         <v>101.96</v>
       </c>
+      <c r="F178" t="s">
+        <v>75</v>
+      </c>
       <c r="H178" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I178" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J178" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L178">
         <v>14.60593126453708</v>
@@ -10862,14 +11396,17 @@
       <c r="D179">
         <v>101.96</v>
       </c>
+      <c r="F179" t="s">
+        <v>75</v>
+      </c>
       <c r="H179" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I179" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J179" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L179">
         <v>15.9019813933336</v>
@@ -10909,14 +11446,17 @@
       <c r="D180">
         <v>101.96</v>
       </c>
+      <c r="F180" t="s">
+        <v>75</v>
+      </c>
       <c r="H180" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I180" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J180" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L180">
         <v>14.06917153020012</v>
@@ -10956,14 +11496,17 @@
       <c r="D181">
         <v>101.96</v>
       </c>
+      <c r="F181" t="s">
+        <v>75</v>
+      </c>
       <c r="H181" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I181" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J181" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L181">
         <v>18.90448104651304</v>
@@ -11003,14 +11546,17 @@
       <c r="D182">
         <v>101.96</v>
       </c>
+      <c r="F182" t="s">
+        <v>75</v>
+      </c>
       <c r="H182" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I182" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J182" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L182">
         <v>16.84948635618693</v>
@@ -11050,14 +11596,17 @@
       <c r="D183">
         <v>101.96</v>
       </c>
+      <c r="F183" t="s">
+        <v>75</v>
+      </c>
       <c r="H183" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I183" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J183" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L183">
         <v>36.42455688920781</v>
@@ -11097,14 +11646,17 @@
       <c r="D184">
         <v>101.96</v>
       </c>
+      <c r="F184" t="s">
+        <v>75</v>
+      </c>
       <c r="H184" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I184" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J184" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L184">
         <v>35.65143064107468</v>
@@ -11144,14 +11696,17 @@
       <c r="D185">
         <v>101.96</v>
       </c>
+      <c r="F185" t="s">
+        <v>75</v>
+      </c>
       <c r="H185" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I185" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J185" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L185">
         <v>34.8025747362314</v>
@@ -11191,14 +11746,17 @@
       <c r="D186">
         <v>101.96</v>
       </c>
+      <c r="F186" t="s">
+        <v>75</v>
+      </c>
       <c r="H186" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I186" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J186" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L186">
         <v>33.52889993282449</v>
@@ -11238,14 +11796,17 @@
       <c r="D187">
         <v>101.96</v>
       </c>
+      <c r="F187" t="s">
+        <v>75</v>
+      </c>
       <c r="H187" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I187" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J187" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L187">
         <v>36.22217852178785</v>
@@ -11285,14 +11846,17 @@
       <c r="D188">
         <v>101.96</v>
       </c>
+      <c r="F188" t="s">
+        <v>75</v>
+      </c>
       <c r="H188" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I188" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J188" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L188">
         <v>36.98173558027523</v>
@@ -11332,14 +11896,17 @@
       <c r="D189">
         <v>101.96</v>
       </c>
+      <c r="F189" t="s">
+        <v>75</v>
+      </c>
       <c r="H189" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I189" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J189" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L189">
         <v>35.0283078096784</v>
@@ -11379,14 +11946,17 @@
       <c r="D190">
         <v>101.96</v>
       </c>
+      <c r="F190" t="s">
+        <v>75</v>
+      </c>
       <c r="H190" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I190" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J190" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L190">
         <v>34.45224195894043</v>
@@ -11426,14 +11996,17 @@
       <c r="D191">
         <v>101.96</v>
       </c>
+      <c r="F191" t="s">
+        <v>75</v>
+      </c>
       <c r="H191" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I191" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J191" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L191">
         <v>37.34133118348795</v>
@@ -11473,14 +12046,17 @@
       <c r="D192">
         <v>101.96</v>
       </c>
+      <c r="F192" t="s">
+        <v>75</v>
+      </c>
       <c r="H192" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I192" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J192" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L192">
         <v>34.55722886372006</v>
@@ -11520,14 +12096,17 @@
       <c r="D193">
         <v>101.96</v>
       </c>
+      <c r="F193" t="s">
+        <v>75</v>
+      </c>
       <c r="H193" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I193" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J193" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L193">
         <v>34.84169132984621</v>
@@ -11567,14 +12146,17 @@
       <c r="D194">
         <v>101.96</v>
       </c>
+      <c r="F194" t="s">
+        <v>75</v>
+      </c>
       <c r="H194" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I194" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J194" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L194">
         <v>40.25535359595114</v>
@@ -11614,14 +12196,17 @@
       <c r="D195">
         <v>101.96</v>
       </c>
+      <c r="F195" t="s">
+        <v>75</v>
+      </c>
       <c r="H195" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I195" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J195" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L195">
         <v>32.535496624289</v>
@@ -11661,14 +12246,17 @@
       <c r="D196">
         <v>101.96</v>
       </c>
+      <c r="F196" t="s">
+        <v>75</v>
+      </c>
       <c r="H196" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I196" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J196" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L196">
         <v>36.55951424677289</v>
@@ -11708,14 +12296,17 @@
       <c r="D197">
         <v>101.96</v>
       </c>
+      <c r="F197" t="s">
+        <v>75</v>
+      </c>
       <c r="H197" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I197" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J197" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L197">
         <v>33.08948085221236</v>
@@ -11755,14 +12346,17 @@
       <c r="D198">
         <v>101.96</v>
       </c>
+      <c r="F198" t="s">
+        <v>75</v>
+      </c>
       <c r="H198" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I198" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J198" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L198">
         <v>32.31431810430986</v>
@@ -11802,14 +12396,17 @@
       <c r="D199">
         <v>101.96</v>
       </c>
+      <c r="F199" t="s">
+        <v>75</v>
+      </c>
       <c r="H199" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I199" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J199" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L199">
         <v>34.13243603061409</v>
@@ -11849,14 +12446,17 @@
       <c r="D200">
         <v>101.96</v>
       </c>
+      <c r="F200" t="s">
+        <v>75</v>
+      </c>
       <c r="H200" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I200" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J200" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L200">
         <v>86.21880949320132</v>
@@ -11896,14 +12496,17 @@
       <c r="D201">
         <v>102.03</v>
       </c>
+      <c r="F201" t="s">
+        <v>75</v>
+      </c>
       <c r="H201" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I201" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J201" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L201">
         <v>14.40453219235653</v>
@@ -11943,14 +12546,17 @@
       <c r="D202">
         <v>102.03</v>
       </c>
+      <c r="F202" t="s">
+        <v>75</v>
+      </c>
       <c r="H202" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I202" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J202" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L202">
         <v>15.22075373954788</v>
@@ -11990,14 +12596,17 @@
       <c r="D203">
         <v>102.03</v>
       </c>
+      <c r="F203" t="s">
+        <v>75</v>
+      </c>
       <c r="H203" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I203" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J203" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L203">
         <v>14.13598827574029</v>
@@ -12037,14 +12646,17 @@
       <c r="D204">
         <v>102.03</v>
       </c>
+      <c r="F204" t="s">
+        <v>75</v>
+      </c>
       <c r="H204" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I204" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J204" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L204">
         <v>14.8889146764632</v>
@@ -12084,14 +12696,17 @@
       <c r="D205">
         <v>102.03</v>
       </c>
+      <c r="F205" t="s">
+        <v>75</v>
+      </c>
       <c r="H205" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I205" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J205" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L205">
         <v>11.3466767561168</v>
@@ -12131,14 +12746,17 @@
       <c r="D206">
         <v>102.03</v>
       </c>
+      <c r="F206" t="s">
+        <v>75</v>
+      </c>
       <c r="H206" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I206" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J206" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L206">
         <v>13.70139727732138</v>
@@ -12178,14 +12796,17 @@
       <c r="D207">
         <v>102.03</v>
       </c>
+      <c r="F207" t="s">
+        <v>75</v>
+      </c>
       <c r="H207" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I207" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J207" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L207">
         <v>17.39217344529752</v>
@@ -12225,14 +12846,17 @@
       <c r="D208">
         <v>102.03</v>
       </c>
+      <c r="F208" t="s">
+        <v>75</v>
+      </c>
       <c r="H208" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I208" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J208" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L208">
         <v>20.07216161178604</v>
@@ -12272,14 +12896,17 @@
       <c r="D209">
         <v>102.03</v>
       </c>
+      <c r="F209" t="s">
+        <v>75</v>
+      </c>
       <c r="H209" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I209" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J209" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L209">
         <v>13.6346728821199</v>
@@ -12319,14 +12946,17 @@
       <c r="D210">
         <v>102.03</v>
       </c>
+      <c r="F210" t="s">
+        <v>75</v>
+      </c>
       <c r="H210" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I210" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J210" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L210">
         <v>22.79049192549948</v>
@@ -12366,14 +12996,17 @@
       <c r="D211">
         <v>102.03</v>
       </c>
+      <c r="F211" t="s">
+        <v>75</v>
+      </c>
       <c r="H211" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I211" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J211" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L211">
         <v>16.31709870909099</v>
@@ -12413,14 +13046,17 @@
       <c r="D212">
         <v>102.03</v>
       </c>
+      <c r="F212" t="s">
+        <v>75</v>
+      </c>
       <c r="H212" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I212" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J212" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L212">
         <v>21.00135857859604</v>
@@ -12460,14 +13096,17 @@
       <c r="D213">
         <v>102.03</v>
       </c>
+      <c r="F213" t="s">
+        <v>75</v>
+      </c>
       <c r="H213" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I213" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J213" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L213">
         <v>19.00770818942219</v>
@@ -12507,14 +13146,17 @@
       <c r="D214">
         <v>102.03</v>
       </c>
+      <c r="F214" t="s">
+        <v>75</v>
+      </c>
       <c r="H214" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I214" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J214" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L214">
         <v>11.68148298748257</v>
@@ -12554,14 +13196,17 @@
       <c r="D215">
         <v>102.03</v>
       </c>
+      <c r="F215" t="s">
+        <v>75</v>
+      </c>
       <c r="H215" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I215" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J215" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L215">
         <v>17.62683922298473</v>
@@ -12601,14 +13246,17 @@
       <c r="D216">
         <v>102.06</v>
       </c>
+      <c r="F216" t="s">
+        <v>75</v>
+      </c>
       <c r="H216" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I216" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J216" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L216">
         <v>32.74721188094824</v>
@@ -12648,14 +13296,17 @@
       <c r="D217">
         <v>102.06</v>
       </c>
+      <c r="F217" t="s">
+        <v>75</v>
+      </c>
       <c r="H217" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I217" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J217" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L217">
         <v>30.93847716411966</v>
@@ -12695,14 +13346,17 @@
       <c r="D218">
         <v>102.06</v>
       </c>
+      <c r="F218" t="s">
+        <v>75</v>
+      </c>
       <c r="H218" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I218" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J218" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L218">
         <v>30.8303972523081</v>
@@ -12742,14 +13396,17 @@
       <c r="D219">
         <v>102.06</v>
       </c>
+      <c r="F219" t="s">
+        <v>75</v>
+      </c>
       <c r="H219" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I219" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J219" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L219">
         <v>27.29509825860648</v>
@@ -12789,14 +13446,17 @@
       <c r="D220">
         <v>102.06</v>
       </c>
+      <c r="F220" t="s">
+        <v>75</v>
+      </c>
       <c r="H220" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I220" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J220" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L220">
         <v>22.51163411822341</v>
@@ -12836,14 +13496,17 @@
       <c r="D221">
         <v>102.06</v>
       </c>
+      <c r="F221" t="s">
+        <v>75</v>
+      </c>
       <c r="H221" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I221" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J221" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L221">
         <v>26.63900200918288</v>
@@ -12883,14 +13546,17 @@
       <c r="D222">
         <v>102.06</v>
       </c>
+      <c r="F222" t="s">
+        <v>75</v>
+      </c>
       <c r="H222" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I222" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J222" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L222">
         <v>26.30410821420157</v>
@@ -12930,14 +13596,17 @@
       <c r="D223">
         <v>102.06</v>
       </c>
+      <c r="F223" t="s">
+        <v>75</v>
+      </c>
       <c r="H223" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I223" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J223" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L223">
         <v>27.81497981726448</v>
@@ -12977,14 +13646,17 @@
       <c r="D224">
         <v>102.06</v>
       </c>
+      <c r="F224" t="s">
+        <v>75</v>
+      </c>
       <c r="H224" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I224" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J224" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L224">
         <v>27.63838907229883</v>
@@ -13024,14 +13696,17 @@
       <c r="D225">
         <v>102.06</v>
       </c>
+      <c r="F225" t="s">
+        <v>75</v>
+      </c>
       <c r="H225" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I225" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J225" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L225">
         <v>30.28123115516652</v>
@@ -13071,14 +13746,17 @@
       <c r="D226">
         <v>102.06</v>
       </c>
+      <c r="F226" t="s">
+        <v>75</v>
+      </c>
       <c r="H226" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I226" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J226" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L226">
         <v>31.02279111875065</v>
@@ -13118,14 +13796,17 @@
       <c r="D227">
         <v>102.06</v>
       </c>
+      <c r="F227" t="s">
+        <v>75</v>
+      </c>
       <c r="H227" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I227" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J227" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L227">
         <v>29.75820944910912</v>
@@ -13165,14 +13846,17 @@
       <c r="D228">
         <v>102.06</v>
       </c>
+      <c r="F228" t="s">
+        <v>75</v>
+      </c>
       <c r="H228" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I228" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J228" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L228">
         <v>31.61701461604629</v>
@@ -13212,14 +13896,17 @@
       <c r="D229">
         <v>102.06</v>
       </c>
+      <c r="F229" t="s">
+        <v>75</v>
+      </c>
       <c r="H229" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I229" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J229" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L229">
         <v>29.68247330192829</v>
@@ -13259,14 +13946,17 @@
       <c r="D230">
         <v>102.06</v>
       </c>
+      <c r="F230" t="s">
+        <v>75</v>
+      </c>
       <c r="H230" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I230" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J230" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L230">
         <v>29.11284318743828</v>
@@ -13306,14 +13996,17 @@
       <c r="D231">
         <v>102.1</v>
       </c>
+      <c r="F231" t="s">
+        <v>75</v>
+      </c>
       <c r="H231" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I231" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J231" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L231">
         <v>7.714586762785332</v>
@@ -13353,14 +14046,17 @@
       <c r="D232">
         <v>102.1</v>
       </c>
+      <c r="F232" t="s">
+        <v>75</v>
+      </c>
       <c r="H232" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I232" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J232" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L232">
         <v>6.834209703790383</v>
@@ -13400,14 +14096,17 @@
       <c r="D233">
         <v>102.1</v>
       </c>
+      <c r="F233" t="s">
+        <v>75</v>
+      </c>
       <c r="H233" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I233" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J233" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L233">
         <v>6.939054268102471</v>
@@ -13447,14 +14146,17 @@
       <c r="D234">
         <v>102.1</v>
       </c>
+      <c r="F234" t="s">
+        <v>75</v>
+      </c>
       <c r="H234" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I234" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J234" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L234">
         <v>8.476382079002827</v>
@@ -13494,14 +14196,17 @@
       <c r="D235">
         <v>102.1</v>
       </c>
+      <c r="F235" t="s">
+        <v>75</v>
+      </c>
       <c r="H235" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I235" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J235" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L235">
         <v>8.844965420070789</v>
@@ -13541,14 +14246,17 @@
       <c r="D236">
         <v>102.1</v>
       </c>
+      <c r="F236" t="s">
+        <v>75</v>
+      </c>
       <c r="H236" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I236" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J236" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L236">
         <v>10.90788126042658</v>
@@ -13588,14 +14296,17 @@
       <c r="D237">
         <v>102.1</v>
       </c>
+      <c r="F237" t="s">
+        <v>75</v>
+      </c>
       <c r="H237" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I237" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J237" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L237">
         <v>10.92670946763253</v>
@@ -13635,14 +14346,17 @@
       <c r="D238">
         <v>102.1</v>
       </c>
+      <c r="F238" t="s">
+        <v>75</v>
+      </c>
       <c r="H238" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I238" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J238" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L238">
         <v>9.824551038897068</v>
@@ -13682,14 +14396,17 @@
       <c r="D239">
         <v>102.1</v>
       </c>
+      <c r="F239" t="s">
+        <v>75</v>
+      </c>
       <c r="H239" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I239" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J239" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L239">
         <v>10.26973305220762</v>
@@ -13729,14 +14446,17 @@
       <c r="D240">
         <v>102.11</v>
       </c>
+      <c r="F240" t="s">
+        <v>75</v>
+      </c>
       <c r="H240" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I240" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J240" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L240">
         <v>13.03942560104074</v>
@@ -13776,14 +14496,17 @@
       <c r="D241">
         <v>102.11</v>
       </c>
+      <c r="F241" t="s">
+        <v>75</v>
+      </c>
       <c r="H241" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I241" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J241" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L241">
         <v>13.32036415233393</v>
@@ -13823,14 +14546,17 @@
       <c r="D242">
         <v>102.11</v>
       </c>
+      <c r="F242" t="s">
+        <v>75</v>
+      </c>
       <c r="H242" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I242" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J242" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L242">
         <v>13.47635175475282</v>
@@ -13870,14 +14596,17 @@
       <c r="D243">
         <v>102.11</v>
       </c>
+      <c r="F243" t="s">
+        <v>75</v>
+      </c>
       <c r="H243" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I243" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J243" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L243">
         <v>13.19939844990029</v>
@@ -13917,14 +14646,17 @@
       <c r="D244">
         <v>102.11</v>
       </c>
+      <c r="F244" t="s">
+        <v>75</v>
+      </c>
       <c r="H244" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I244" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J244" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L244">
         <v>12.99837369211979</v>
@@ -13964,14 +14696,17 @@
       <c r="D245">
         <v>102.11</v>
       </c>
+      <c r="F245" t="s">
+        <v>75</v>
+      </c>
       <c r="H245" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I245" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J245" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L245">
         <v>14.54756485642743</v>
@@ -14011,14 +14746,17 @@
       <c r="D246">
         <v>102.11</v>
       </c>
+      <c r="F246" t="s">
+        <v>75</v>
+      </c>
       <c r="H246" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I246" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J246" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L246">
         <v>13.61867391898239</v>
@@ -14058,14 +14796,17 @@
       <c r="D247">
         <v>102.11</v>
       </c>
+      <c r="F247" t="s">
+        <v>75</v>
+      </c>
       <c r="H247" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I247" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J247" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L247">
         <v>14.09925239986907</v>
@@ -14105,14 +14846,17 @@
       <c r="D248">
         <v>102.11</v>
       </c>
+      <c r="F248" t="s">
+        <v>75</v>
+      </c>
       <c r="H248" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I248" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J248" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L248">
         <v>13.05290719066591</v>
@@ -14152,14 +14896,17 @@
       <c r="D249">
         <v>102.11</v>
       </c>
+      <c r="F249" t="s">
+        <v>75</v>
+      </c>
       <c r="H249" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I249" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J249" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L249">
         <v>15.22230999493526</v>
@@ -14199,14 +14946,17 @@
       <c r="D250">
         <v>102.11</v>
       </c>
+      <c r="F250" t="s">
+        <v>75</v>
+      </c>
       <c r="H250" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I250" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J250" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L250">
         <v>15.01927606268011</v>
@@ -14246,14 +14996,17 @@
       <c r="D251">
         <v>102.11</v>
       </c>
+      <c r="F251" t="s">
+        <v>75</v>
+      </c>
       <c r="H251" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I251" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J251" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L251">
         <v>12.56067029663772</v>
@@ -14293,14 +15046,17 @@
       <c r="D252">
         <v>102.11</v>
       </c>
+      <c r="F252" t="s">
+        <v>75</v>
+      </c>
       <c r="H252" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I252" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J252" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L252">
         <v>15.3170598000188</v>
@@ -14340,14 +15096,17 @@
       <c r="D253">
         <v>102.11</v>
       </c>
+      <c r="F253" t="s">
+        <v>75</v>
+      </c>
       <c r="H253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I253" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J253" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L253">
         <v>14.64853883367337</v>
@@ -14387,14 +15146,17 @@
       <c r="D254">
         <v>102.14</v>
       </c>
+      <c r="F254" t="s">
+        <v>75</v>
+      </c>
       <c r="H254" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I254" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J254" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L254">
         <v>36.54636448163497</v>
@@ -14434,14 +15196,17 @@
       <c r="D255">
         <v>102.14</v>
       </c>
+      <c r="F255" t="s">
+        <v>75</v>
+      </c>
       <c r="H255" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I255" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J255" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L255">
         <v>36.91116957367485</v>
@@ -14481,14 +15246,17 @@
       <c r="D256">
         <v>102.14</v>
       </c>
+      <c r="F256" t="s">
+        <v>75</v>
+      </c>
       <c r="H256" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I256" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J256" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L256">
         <v>36.19966659339396</v>
@@ -14528,14 +15296,17 @@
       <c r="D257">
         <v>102.14</v>
       </c>
+      <c r="F257" t="s">
+        <v>75</v>
+      </c>
       <c r="H257" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I257" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J257" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L257">
         <v>40.24115324510513</v>
@@ -14575,14 +15346,17 @@
       <c r="D258">
         <v>102.14</v>
       </c>
+      <c r="F258" t="s">
+        <v>75</v>
+      </c>
       <c r="H258" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I258" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J258" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L258">
         <v>38.72279380509821</v>
@@ -14622,14 +15396,17 @@
       <c r="D259">
         <v>102.14</v>
       </c>
+      <c r="F259" t="s">
+        <v>75</v>
+      </c>
       <c r="H259" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I259" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J259" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L259">
         <v>40.31533485161798</v>
@@ -14669,14 +15446,17 @@
       <c r="D260">
         <v>102.14</v>
       </c>
+      <c r="F260" t="s">
+        <v>75</v>
+      </c>
       <c r="H260" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I260" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J260" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L260">
         <v>12.88040345487666</v>
@@ -14716,14 +15496,17 @@
       <c r="D261">
         <v>102.14</v>
       </c>
+      <c r="F261" t="s">
+        <v>75</v>
+      </c>
       <c r="H261" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I261" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J261" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L261">
         <v>13.14417209856799</v>
@@ -14763,14 +15546,17 @@
       <c r="D262">
         <v>102.14</v>
       </c>
+      <c r="F262" t="s">
+        <v>75</v>
+      </c>
       <c r="H262" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I262" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J262" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L262">
         <v>12.91474619142749</v>
@@ -14810,14 +15596,17 @@
       <c r="D263">
         <v>102.14</v>
       </c>
+      <c r="F263" t="s">
+        <v>75</v>
+      </c>
       <c r="H263" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I263" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J263" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L263">
         <v>13.47757547723624</v>
@@ -14857,14 +15646,17 @@
       <c r="D264">
         <v>102.14</v>
       </c>
+      <c r="F264" t="s">
+        <v>75</v>
+      </c>
       <c r="H264" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I264" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J264" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L264">
         <v>13.70696881978566</v>
@@ -14904,14 +15696,17 @@
       <c r="D265">
         <v>102.14</v>
       </c>
+      <c r="F265" t="s">
+        <v>75</v>
+      </c>
       <c r="H265" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I265" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J265" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L265">
         <v>15.97676707560944</v>
@@ -14951,14 +15746,17 @@
       <c r="D266">
         <v>102.14</v>
       </c>
+      <c r="F266" t="s">
+        <v>75</v>
+      </c>
       <c r="H266" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I266" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J266" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L266">
         <v>17.89603042009682</v>
@@ -14998,14 +15796,17 @@
       <c r="D267">
         <v>102.14</v>
       </c>
+      <c r="F267" t="s">
+        <v>75</v>
+      </c>
       <c r="H267" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I267" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J267" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L267">
         <v>28.28281690740773</v>
@@ -15045,14 +15846,17 @@
       <c r="D268">
         <v>102.14</v>
       </c>
+      <c r="F268" t="s">
+        <v>75</v>
+      </c>
       <c r="H268" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I268" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J268" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L268">
         <v>26.94461880375358</v>
@@ -15092,14 +15896,17 @@
       <c r="D269">
         <v>102.14</v>
       </c>
+      <c r="F269" t="s">
+        <v>75</v>
+      </c>
       <c r="H269" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I269" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J269" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L269">
         <v>12.07341603011859</v>
@@ -15139,14 +15946,17 @@
       <c r="D270">
         <v>102.22</v>
       </c>
+      <c r="F270" t="s">
+        <v>75</v>
+      </c>
       <c r="H270" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I270" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J270" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L270">
         <v>3.362111045531387</v>
@@ -15186,14 +15996,17 @@
       <c r="D271">
         <v>102.22</v>
       </c>
+      <c r="F271" t="s">
+        <v>75</v>
+      </c>
       <c r="H271" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I271" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J271" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L271">
         <v>3.3178589281041</v>
@@ -15233,14 +16046,17 @@
       <c r="D272">
         <v>102.22</v>
       </c>
+      <c r="F272" t="s">
+        <v>75</v>
+      </c>
       <c r="H272" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I272" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J272" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L272">
         <v>3.077803120642113</v>
@@ -15280,14 +16096,17 @@
       <c r="D273">
         <v>102.22</v>
       </c>
+      <c r="F273" t="s">
+        <v>75</v>
+      </c>
       <c r="H273" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I273" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J273" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L273">
         <v>2.593011319018456</v>
@@ -15327,14 +16146,17 @@
       <c r="D274">
         <v>102.22</v>
       </c>
+      <c r="F274" t="s">
+        <v>75</v>
+      </c>
       <c r="H274" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I274" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J274" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="L274">
         <v>3.203398062720459</v>
@@ -15374,14 +16196,17 @@
       <c r="D275">
         <v>102.22</v>
       </c>
+      <c r="F275" t="s">
+        <v>75</v>
+      </c>
       <c r="H275" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I275" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J275" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L275">
         <v>3.052490446505272</v>
@@ -15421,14 +16246,17 @@
       <c r="D276">
         <v>102.22</v>
       </c>
+      <c r="F276" t="s">
+        <v>75</v>
+      </c>
       <c r="H276" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I276" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J276" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L276">
         <v>2.667766128903645</v>
@@ -15468,14 +16296,17 @@
       <c r="D277">
         <v>102.22</v>
       </c>
+      <c r="F277" t="s">
+        <v>75</v>
+      </c>
       <c r="H277" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I277" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J277" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L277">
         <v>2.653854941572961</v>
@@ -15515,14 +16346,17 @@
       <c r="D278">
         <v>102.22</v>
       </c>
+      <c r="F278" t="s">
+        <v>75</v>
+      </c>
       <c r="H278" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I278" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J278" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L278">
         <v>2.694607575851763</v>
@@ -15562,14 +16396,17 @@
       <c r="D279">
         <v>102.22</v>
       </c>
+      <c r="F279" t="s">
+        <v>75</v>
+      </c>
       <c r="H279" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I279" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J279" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L279">
         <v>2.647626007823968</v>
@@ -15609,14 +16446,17 @@
       <c r="D280">
         <v>102.22</v>
       </c>
+      <c r="F280" t="s">
+        <v>75</v>
+      </c>
       <c r="H280" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I280" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J280" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="L280">
         <v>3.537434851927873</v>
@@ -15647,6 +16487,9 @@
       </c>
     </row>
     <row r="281" spans="2:30">
+      <c r="F281" t="s">
+        <v>75</v>
+      </c>
       <c r="L281">
         <v>0</v>
       </c>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/after_conversion_xian_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI-Xianshuihe_Datenbank/after_conversion_xian_mapped_readable.xlsx
@@ -16493,6 +16493,9 @@
       <c r="L281">
         <v>0</v>
       </c>
+      <c r="AD281">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
